--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4905,10 +4905,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -4927,35 +4927,45 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -4971,43 +4981,27 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -5024,14 +5018,6 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -5040,33 +5026,47 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -5091,7 +5091,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5103,7 +5139,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5115,19 +5151,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5139,7 +5187,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5157,13 +5235,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5175,79 +5247,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5265,13 +5271,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5282,21 +5282,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -5318,8 +5303,17 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5339,22 +5333,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5376,9 +5365,20 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5390,145 +5390,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="4"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2037" uniqueCount="1444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2038" uniqueCount="1444">
   <si>
     <t>Id</t>
   </si>
@@ -1175,7 +1175,7 @@
   </si>
   <si>
     <t>(条件)自身の攻撃時
-一度だけ自身の攻撃を必中にする</t>
+一度だけ\sの命中率が/f[f,0,3]%アップ</t>
   </si>
   <si>
     <t>Eagle Eye</t>
@@ -3262,10 +3262,10 @@
 Permanently increase \s's SPD by /f[f,0,3].</t>
   </si>
   <si>
-    <t>バトルで得るExp+20%</t>
-  </si>
-  <si>
-    <t>Increase EXP gained in battle by 20%.</t>
+    <t>バトルで得るExp+10%</t>
+  </si>
+  <si>
+    <t>Increase EXP gained in battle by 10%.</t>
   </si>
   <si>
     <t>セブンズストーン</t>
@@ -4907,8 +4907,8 @@
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -4927,7 +4927,60 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4941,10 +4994,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4957,10 +5011,46 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4977,96 +5067,6 @@
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -5091,7 +5091,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5103,7 +5115,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5115,7 +5139,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5127,7 +5193,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5139,13 +5229,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5157,55 +5259,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5217,61 +5271,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5282,6 +5282,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -5300,39 +5309,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -5344,21 +5320,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5382,6 +5343,45 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -5390,145 +5390,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -44374,7 +44374,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:9">
       <c r="A105">
         <v>11020</v>
       </c>
@@ -44390,16 +44390,19 @@
         <v>ステート付与</v>
       </c>
       <c r="E105">
-        <v>2240</v>
+        <v>1080</v>
       </c>
       <c r="F105">
         <v>1</v>
       </c>
       <c r="G105">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H105">
         <v>100</v>
+      </c>
+      <c r="I105" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -46324,7 +46327,7 @@
         <v>Hp回復</v>
       </c>
       <c r="E170">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F170">
         <v>0</v>
@@ -51269,7 +51272,7 @@
         <v>獲得Eｘｐ％アップ</v>
       </c>
       <c r="E339">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F339">
         <v>0</v>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4899,10 +4899,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -4920,23 +4920,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4951,6 +4943,14 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -4958,9 +4958,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4983,6 +4982,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -4990,36 +4996,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5027,7 +5004,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5042,7 +5019,38 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5051,14 +5059,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5085,7 +5085,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5097,13 +5145,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5121,85 +5217,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5217,55 +5235,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5276,6 +5276,66 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -5297,71 +5357,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5384,7 +5384,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5393,136 +5393,136 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -21624,7 +21624,7 @@
         <v>0</v>
       </c>
       <c r="K135">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L135">
         <v>20</v>
@@ -46237,7 +46237,7 @@
         <v>Hp回復</v>
       </c>
       <c r="E167">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F167">
         <v>0</v>
@@ -46265,7 +46265,7 @@
         <v>Hp回復</v>
       </c>
       <c r="E168">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F168">
         <v>0</v>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -3282,8 +3282,8 @@
     <t>ヒールユニット</t>
   </si>
   <si>
-    <t>(条件)所持していると自動で効果を発揮
-移動時に1マス間隔でHpを1回復</t>
+    <t>(条件)未開示のマスに移動した時
+Hpを1回復</t>
   </si>
   <si>
     <t>Heal Unit</t>
@@ -4905,10 +4905,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -4927,36 +4927,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4970,7 +4941,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4979,6 +4957,52 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4993,7 +5017,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -5001,30 +5025,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5038,8 +5039,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -5047,7 +5055,7 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -5056,15 +5064,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5091,13 +5091,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5109,7 +5127,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5121,103 +5145,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5235,7 +5175,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5247,31 +5265,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5285,17 +5285,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5319,27 +5319,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5362,23 +5357,28 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5390,145 +5390,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -60320,10 +60320,10 @@
         <v>1</v>
       </c>
       <c r="F187">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G187">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H187">
         <v>0</v>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="4"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -3311,18 +3311,18 @@
 Allow \s to take a little preemptive action.</t>
   </si>
   <si>
-    <t>先陣の心得</t>
-  </si>
-  <si>
-    <t>(条件)バトル開始時
-必ず先制攻撃ができる</t>
-  </si>
-  <si>
-    <t>Foremost Knowledge</t>
-  </si>
-  <si>
-    <t>(Condition: At battle start)
-Can always perform a preemptive attack.</t>
+    <t>黄金の守護精霊</t>
+  </si>
+  <si>
+    <t>(条件)Period経過時
+ランダムで換金アイテムを1つ入手</t>
+  </si>
+  <si>
+    <t>Golden Spirit</t>
+  </si>
+  <si>
+    <t>(Condition: After a Period passes)
+Randomly obtain one Sellable item.</t>
   </si>
   <si>
     <t>ヒスイの勾玉</t>
@@ -5050,10 +5050,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -5071,14 +5071,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -5086,15 +5078,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5108,9 +5094,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5118,14 +5103,21 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5140,14 +5132,46 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5161,14 +5185,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -5176,11 +5192,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -5192,24 +5207,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5236,7 +5236,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5248,7 +5272,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5260,7 +5326,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5272,55 +5398,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5332,91 +5416,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5427,6 +5427,17 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -5447,26 +5458,27 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5486,29 +5498,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5535,145 +5535,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -30994,7 +30994,7 @@
       </c>
       <c r="C248" t="str">
         <f>INDEX(TextData!B:B,MATCH(B248,TextData!A:A))</f>
-        <v>先陣の心得</v>
+        <v>黄金の守護精霊</v>
       </c>
       <c r="D248">
         <v>6</v>
@@ -53536,20 +53536,20 @@
       </c>
       <c r="B346" t="str">
         <f>INDEX(TextData!B:B,MATCH(A346,TextData!A:A))</f>
-        <v>先陣の心得</v>
+        <v>黄金の守護精霊</v>
       </c>
       <c r="C346">
-        <v>5040</v>
+        <v>40010</v>
       </c>
       <c r="D346" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C346,Define!P:P))</f>
-        <v>先制攻撃</v>
+        <v>アイテム入手</v>
       </c>
       <c r="E346">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F346">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G346">
         <v>0</v>
@@ -63178,14 +63178,14 @@
       </c>
       <c r="B183" t="str">
         <f>INDEX(TextData!B:B,MATCH(A183,TextData!A:A))</f>
-        <v>先陣の心得</v>
+        <v>黄金の守護精霊</v>
       </c>
       <c r="C183">
-        <v>0</v>
+        <v>40020</v>
       </c>
       <c r="D183" t="str">
         <f>INDEX(Define!V:V,MATCH(C183,Define!U:U))</f>
-        <v>なし</v>
+        <v>ピリオド経過</v>
       </c>
       <c r="E183">
         <v>1</v>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -469,7 +469,7 @@
   <si>
     <t>\sにATKx/f[f,0,1]%ダメージ
 \sに/f[f,1,2]ターン回避率/f[f,1,3]%ダウンを付与
-自身に/f[f,3,2]ターン回避率/f[f,3,3]%アップを付与</t>
+自身に/f[f,1,2]ターン回避率/f[f,1,3]%アップを付与</t>
   </si>
   <si>
     <t>Spriral Sword</t>
@@ -1509,22 +1509,6 @@
     <t>Cure Stun</t>
   </si>
   <si>
-    <t>ソーサリーコネクト</t>
-  </si>
-  <si>
-    <t>(条件)他の味方が攻撃する直前に発動
-2ターンの間
-\sのATKを/f[f,0,3]アップし自身のATKを/f[f,0,3]ダウン</t>
-  </si>
-  <si>
-    <t>Sorcery Connect</t>
-  </si>
-  <si>
-    <t>(Condition: Just before another ally attacks)
-For 2 turns, increase \s's ATK by /f[f,0,3]
-and decrease own ATK by /f[f,0,3].</t>
-  </si>
-  <si>
     <t>アウトオブオーダー</t>
   </si>
   <si>
@@ -1797,6 +1781,20 @@
   <si>
     <t>(Condition: Before taking an action)
 Restore HP by /f[f,0,3]% of damage taken.</t>
+  </si>
+  <si>
+    <t>クイックバリア</t>
+  </si>
+  <si>
+    <t>(条件)味方が攻撃を受ける直前
+対象のダメージを/f[f,0,3]%カット</t>
+  </si>
+  <si>
+    <t>Quick Barrier</t>
+  </si>
+  <si>
+    <t>(Condition: Just before an ally is attacked)
+Reduce damage taken by target by /f[f,0,3]%.</t>
   </si>
   <si>
     <t>ルミナスカバー</t>
@@ -1864,20 +1862,6 @@
 /s</t>
   </si>
   <si>
-    <t>クイックバリア</t>
-  </si>
-  <si>
-    <t>(条件)味方が攻撃を受ける直前
-対象のダメージを/f[f,0,3]%カット</t>
-  </si>
-  <si>
-    <t>Quick Barrier</t>
-  </si>
-  <si>
-    <t>(Condition: Just before an ally is attacked)
-Reduce damage taken by target by /f[f,0,3]%.</t>
-  </si>
-  <si>
     <t>クイックキュア</t>
   </si>
   <si>
@@ -2281,6 +2265,22 @@
   <si>
     <t>(Condition: When self is attacked)
 Increase \s's ATK and DEF by /f[f,0,3] for /f[f,0,2] turns.</t>
+  </si>
+  <si>
+    <t>ソーサリーコネクト</t>
+  </si>
+  <si>
+    <t>(条件)他の味方が攻撃する直前に発動
+2ターンの間
+\sのATKを/f[f,0,3]アップし自身のATKを/f[f,0,3]ダウン</t>
+  </si>
+  <si>
+    <t>Sorcery Connect</t>
+  </si>
+  <si>
+    <t>(Condition: Just before another ally attacks)
+For 2 turns, increase \s's ATK by /f[f,0,3]
+and decrease own ATK by /f[f,0,3].</t>
   </si>
   <si>
     <t>リープリアクト</t>
@@ -5050,10 +5050,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -5071,21 +5071,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -5094,21 +5079,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -5117,9 +5088,31 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -5132,7 +5125,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5147,7 +5148,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5155,45 +5156,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5209,7 +5179,37 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5236,13 +5236,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5254,103 +5392,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5362,55 +5404,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5430,17 +5430,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -5452,33 +5441,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5498,17 +5460,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5527,6 +5483,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -5535,7 +5535,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5544,136 +5544,136 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -19453,14 +19453,14 @@
     </row>
     <row r="107" spans="1:24">
       <c r="A107">
-        <v>12070</v>
+        <v>12090</v>
       </c>
       <c r="B107">
-        <v>12070</v>
+        <v>12090</v>
       </c>
       <c r="C107" t="str">
         <f>INDEX(TextData!B:B,MATCH(B107,TextData!A:A))</f>
-        <v>ソーサリーコネクト</v>
+        <v>アウトオブオーダー</v>
       </c>
       <c r="D107">
         <v>6</v>
@@ -19470,11 +19470,11 @@
         <v>自己強化</v>
       </c>
       <c r="F107">
-        <v>3005</v>
+        <v>1501</v>
       </c>
       <c r="G107" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F107,[1]Animations!A:A))</f>
-        <v>Genfulew_Effect/B&amp;S_MinMax_AttackUp</v>
+        <v>MakerEffect/BallsOfLight</v>
       </c>
       <c r="H107">
         <v>1</v>
@@ -19487,7 +19487,7 @@
         <v>0</v>
       </c>
       <c r="K107">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L107">
         <v>20</v>
@@ -19507,21 +19507,21 @@
         <v>パッシブ</v>
       </c>
       <c r="Q107">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="R107" t="str">
         <f>INDEX(Define!K:K,MATCH(Q107,Define!J:J))</f>
-        <v>Triggerの条件を満たす</v>
+        <v>自身</v>
       </c>
       <c r="S107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T107" t="str">
         <f>INDEX(Define!N:N,MATCH(S107,Define!M:M))</f>
-        <v>単体</v>
+        <v>列</v>
       </c>
       <c r="U107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V107">
         <v>1</v>
@@ -19530,19 +19530,19 @@
         <v>1</v>
       </c>
       <c r="X107">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:24">
       <c r="A108">
-        <v>12071</v>
+        <v>12100</v>
       </c>
       <c r="B108">
-        <v>12070</v>
+        <v>12100</v>
       </c>
       <c r="C108" t="str">
         <f>INDEX(TextData!B:B,MATCH(B108,TextData!A:A))</f>
-        <v>ソーサリーコネクト</v>
+        <v>ワンスパニッシュ</v>
       </c>
       <c r="D108">
         <v>6</v>
@@ -19552,11 +19552,11 @@
         <v>自己強化</v>
       </c>
       <c r="F108">
-        <v>3006</v>
+        <v>1109</v>
       </c>
       <c r="G108" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F108,[1]Animations!A:A))</f>
-        <v>Genfulew_Effect/B&amp;S_MinMax_AttackDown</v>
+        <v>MakerEffect/Flash</v>
       </c>
       <c r="H108">
         <v>1</v>
@@ -19569,10 +19569,10 @@
         <v>0</v>
       </c>
       <c r="K108">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L108">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M108">
         <v>2</v>
@@ -19617,14 +19617,14 @@
     </row>
     <row r="109" spans="1:24">
       <c r="A109">
-        <v>12090</v>
+        <v>12110</v>
       </c>
       <c r="B109">
-        <v>12090</v>
+        <v>12110</v>
       </c>
       <c r="C109" t="str">
         <f>INDEX(TextData!B:B,MATCH(B109,TextData!A:A))</f>
-        <v>アウトオブオーダー</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="D109">
         <v>6</v>
@@ -19634,11 +19634,11 @@
         <v>自己強化</v>
       </c>
       <c r="F109">
-        <v>1501</v>
+        <v>1109</v>
       </c>
       <c r="G109" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F109,[1]Animations!A:A))</f>
-        <v>MakerEffect/BallsOfLight</v>
+        <v>MakerEffect/Flash</v>
       </c>
       <c r="H109">
         <v>1</v>
@@ -19654,7 +19654,7 @@
         <v>0</v>
       </c>
       <c r="L109">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M109">
         <v>2</v>
@@ -19678,14 +19678,14 @@
         <v>自身</v>
       </c>
       <c r="S109">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T109" t="str">
         <f>INDEX(Define!N:N,MATCH(S109,Define!M:M))</f>
-        <v>列</v>
+        <v>自身</v>
       </c>
       <c r="U109">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V109">
         <v>1</v>
@@ -19699,14 +19699,14 @@
     </row>
     <row r="110" spans="1:24">
       <c r="A110">
-        <v>12100</v>
+        <v>12120</v>
       </c>
       <c r="B110">
-        <v>12100</v>
+        <v>12120</v>
       </c>
       <c r="C110" t="str">
         <f>INDEX(TextData!B:B,MATCH(B110,TextData!A:A))</f>
-        <v>ワンスパニッシュ</v>
+        <v>パリィ</v>
       </c>
       <c r="D110">
         <v>6</v>
@@ -19733,10 +19733,10 @@
         <v>0</v>
       </c>
       <c r="K110">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L110">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M110">
         <v>2</v>
@@ -19781,14 +19781,14 @@
     </row>
     <row r="111" spans="1:24">
       <c r="A111">
-        <v>12110</v>
+        <v>12130</v>
       </c>
       <c r="B111">
-        <v>12110</v>
+        <v>12130</v>
       </c>
       <c r="C111" t="str">
         <f>INDEX(TextData!B:B,MATCH(B111,TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>チェイスマジック</v>
       </c>
       <c r="D111">
         <v>6</v>
@@ -19815,7 +19815,7 @@
         <v>0</v>
       </c>
       <c r="K111">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L111">
         <v>30</v>
@@ -19835,21 +19835,21 @@
         <v>パッシブ</v>
       </c>
       <c r="Q111">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R111" t="str">
         <f>INDEX(Define!K:K,MATCH(Q111,Define!J:J))</f>
-        <v>自身</v>
+        <v>追撃</v>
       </c>
       <c r="S111">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T111" t="str">
         <f>INDEX(Define!N:N,MATCH(S111,Define!M:M))</f>
-        <v>自身</v>
+        <v>単体</v>
       </c>
       <c r="U111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V111">
         <v>1</v>
@@ -19863,14 +19863,14 @@
     </row>
     <row r="112" spans="1:24">
       <c r="A112">
-        <v>12120</v>
+        <v>12140</v>
       </c>
       <c r="B112">
-        <v>12120</v>
+        <v>12140</v>
       </c>
       <c r="C112" t="str">
         <f>INDEX(TextData!B:B,MATCH(B112,TextData!A:A))</f>
-        <v>パリィ</v>
+        <v>ウィンドライズ</v>
       </c>
       <c r="D112">
         <v>6</v>
@@ -19880,11 +19880,11 @@
         <v>自己強化</v>
       </c>
       <c r="F112">
-        <v>1109</v>
+        <v>1501</v>
       </c>
       <c r="G112" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F112,[1]Animations!A:A))</f>
-        <v>MakerEffect/Flash</v>
+        <v>MakerEffect/BallsOfLight</v>
       </c>
       <c r="H112">
         <v>1</v>
@@ -19897,7 +19897,7 @@
         <v>0</v>
       </c>
       <c r="K112">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L112">
         <v>30</v>
@@ -19917,21 +19917,21 @@
         <v>パッシブ</v>
       </c>
       <c r="Q112">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R112" t="str">
         <f>INDEX(Define!K:K,MATCH(Q112,Define!J:J))</f>
-        <v>自身</v>
+        <v>反撃</v>
       </c>
       <c r="S112">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T112" t="str">
         <f>INDEX(Define!N:N,MATCH(S112,Define!M:M))</f>
-        <v>自身</v>
+        <v>単体</v>
       </c>
       <c r="U112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V112">
         <v>1</v>
@@ -19945,14 +19945,14 @@
     </row>
     <row r="113" spans="1:24">
       <c r="A113">
-        <v>12130</v>
+        <v>12510</v>
       </c>
       <c r="B113">
-        <v>12130</v>
+        <v>12510</v>
       </c>
       <c r="C113" t="str">
         <f>INDEX(TextData!B:B,MATCH(B113,TextData!A:A))</f>
-        <v>チェイスマジック</v>
+        <v>アクトスタンス</v>
       </c>
       <c r="D113">
         <v>6</v>
@@ -19979,7 +19979,7 @@
         <v>0</v>
       </c>
       <c r="K113">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L113">
         <v>30</v>
@@ -19999,21 +19999,21 @@
         <v>パッシブ</v>
       </c>
       <c r="Q113">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R113" t="str">
         <f>INDEX(Define!K:K,MATCH(Q113,Define!J:J))</f>
-        <v>追撃</v>
+        <v>自身</v>
       </c>
       <c r="S113">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T113" t="str">
         <f>INDEX(Define!N:N,MATCH(S113,Define!M:M))</f>
-        <v>単体</v>
+        <v>自身</v>
       </c>
       <c r="U113">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V113">
         <v>1</v>
@@ -20027,14 +20027,14 @@
     </row>
     <row r="114" spans="1:24">
       <c r="A114">
-        <v>12140</v>
+        <v>12910</v>
       </c>
       <c r="B114">
-        <v>12140</v>
+        <v>12910</v>
       </c>
       <c r="C114" t="str">
         <f>INDEX(TextData!B:B,MATCH(B114,TextData!A:A))</f>
-        <v>ウィンドライズ</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="D114">
         <v>6</v>
@@ -20081,21 +20081,21 @@
         <v>パッシブ</v>
       </c>
       <c r="Q114">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R114" t="str">
         <f>INDEX(Define!K:K,MATCH(Q114,Define!J:J))</f>
-        <v>反撃</v>
+        <v>自身</v>
       </c>
       <c r="S114">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T114" t="str">
         <f>INDEX(Define!N:N,MATCH(S114,Define!M:M))</f>
-        <v>単体</v>
+        <v>自身</v>
       </c>
       <c r="U114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V114">
         <v>1</v>
@@ -20109,14 +20109,14 @@
     </row>
     <row r="115" spans="1:24">
       <c r="A115">
-        <v>12510</v>
+        <v>12930</v>
       </c>
       <c r="B115">
-        <v>12510</v>
+        <v>12930</v>
       </c>
       <c r="C115" t="str">
         <f>INDEX(TextData!B:B,MATCH(B115,TextData!A:A))</f>
-        <v>アクトスタンス</v>
+        <v>スウィフトカレント</v>
       </c>
       <c r="D115">
         <v>6</v>
@@ -20126,11 +20126,11 @@
         <v>自己強化</v>
       </c>
       <c r="F115">
-        <v>1109</v>
+        <v>1501</v>
       </c>
       <c r="G115" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F115,[1]Animations!A:A))</f>
-        <v>MakerEffect/Flash</v>
+        <v>MakerEffect/BallsOfLight</v>
       </c>
       <c r="H115">
         <v>1</v>
@@ -20191,14 +20191,14 @@
     </row>
     <row r="116" spans="1:24">
       <c r="A116">
-        <v>12910</v>
+        <v>12940</v>
       </c>
       <c r="B116">
-        <v>12910</v>
+        <v>12940</v>
       </c>
       <c r="C116" t="str">
         <f>INDEX(TextData!B:B,MATCH(B116,TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>イヴェイドオール</v>
       </c>
       <c r="D116">
         <v>6</v>
@@ -20245,18 +20245,18 @@
         <v>パッシブ</v>
       </c>
       <c r="Q116">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R116" t="str">
         <f>INDEX(Define!K:K,MATCH(Q116,Define!J:J))</f>
-        <v>自身</v>
+        <v>味方</v>
       </c>
       <c r="S116">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T116" t="str">
         <f>INDEX(Define!N:N,MATCH(S116,Define!M:M))</f>
-        <v>自身</v>
+        <v>列</v>
       </c>
       <c r="U116">
         <v>1</v>
@@ -20273,14 +20273,14 @@
     </row>
     <row r="117" spans="1:24">
       <c r="A117">
-        <v>12930</v>
+        <v>13010</v>
       </c>
       <c r="B117">
-        <v>12930</v>
+        <v>13010</v>
       </c>
       <c r="C117" t="str">
         <f>INDEX(TextData!B:B,MATCH(B117,TextData!A:A))</f>
-        <v>スウィフトカレント</v>
+        <v>ヘビィカバー</v>
       </c>
       <c r="D117">
         <v>6</v>
@@ -20290,11 +20290,11 @@
         <v>自己強化</v>
       </c>
       <c r="F117">
-        <v>1501</v>
+        <v>1109</v>
       </c>
       <c r="G117" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F117,[1]Animations!A:A))</f>
-        <v>MakerEffect/BallsOfLight</v>
+        <v>MakerEffect/Flash</v>
       </c>
       <c r="H117">
         <v>1</v>
@@ -20307,17 +20307,17 @@
         <v>0</v>
       </c>
       <c r="K117">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L117">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M117">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N117" t="str">
         <f>INDEX(Define!E:E,MATCH(M117,Define!D:D))</f>
-        <v>雷</v>
+        <v>氷</v>
       </c>
       <c r="O117">
         <v>2</v>
@@ -20327,18 +20327,18 @@
         <v>パッシブ</v>
       </c>
       <c r="Q117">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R117" t="str">
         <f>INDEX(Define!K:K,MATCH(Q117,Define!J:J))</f>
-        <v>自身</v>
+        <v>味方</v>
       </c>
       <c r="S117">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T117" t="str">
         <f>INDEX(Define!N:N,MATCH(S117,Define!M:M))</f>
-        <v>自身</v>
+        <v>単体・自身を除く</v>
       </c>
       <c r="U117">
         <v>1</v>
@@ -20355,14 +20355,14 @@
     </row>
     <row r="118" spans="1:24">
       <c r="A118">
-        <v>12940</v>
+        <v>13011</v>
       </c>
       <c r="B118">
-        <v>12940</v>
+        <v>13010</v>
       </c>
       <c r="C118" t="str">
         <f>INDEX(TextData!B:B,MATCH(B118,TextData!A:A))</f>
-        <v>イヴェイドオール</v>
+        <v>ヘビィカバー</v>
       </c>
       <c r="D118">
         <v>6</v>
@@ -20372,11 +20372,11 @@
         <v>自己強化</v>
       </c>
       <c r="F118">
-        <v>1501</v>
+        <v>803</v>
       </c>
       <c r="G118" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F118,[1]Animations!A:A))</f>
-        <v>MakerEffect/BallsOfLight</v>
+        <v>MakerEffect/Powerup3</v>
       </c>
       <c r="H118">
         <v>1</v>
@@ -20389,17 +20389,17 @@
         <v>0</v>
       </c>
       <c r="K118">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L118">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M118">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N118" t="str">
         <f>INDEX(Define!E:E,MATCH(M118,Define!D:D))</f>
-        <v>雷</v>
+        <v>氷</v>
       </c>
       <c r="O118">
         <v>2</v>
@@ -20409,18 +20409,18 @@
         <v>パッシブ</v>
       </c>
       <c r="Q118">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R118" t="str">
         <f>INDEX(Define!K:K,MATCH(Q118,Define!J:J))</f>
-        <v>味方</v>
+        <v>自身</v>
       </c>
       <c r="S118">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T118" t="str">
         <f>INDEX(Define!N:N,MATCH(S118,Define!M:M))</f>
-        <v>列</v>
+        <v>自身</v>
       </c>
       <c r="U118">
         <v>1</v>
@@ -20437,14 +20437,14 @@
     </row>
     <row r="119" spans="1:24">
       <c r="A119">
-        <v>13010</v>
+        <v>13020</v>
       </c>
       <c r="B119">
-        <v>13010</v>
+        <v>13020</v>
       </c>
       <c r="C119" t="str">
         <f>INDEX(TextData!B:B,MATCH(B119,TextData!A:A))</f>
-        <v>ヘビィカバー</v>
+        <v>アイシクルエッジ</v>
       </c>
       <c r="D119">
         <v>6</v>
@@ -20454,11 +20454,11 @@
         <v>自己強化</v>
       </c>
       <c r="F119">
-        <v>1109</v>
+        <v>1024</v>
       </c>
       <c r="G119" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F119,[1]Animations!A:A))</f>
-        <v>MakerEffect/Flash</v>
+        <v>MakerEffect/PierceIce</v>
       </c>
       <c r="H119">
         <v>1</v>
@@ -20471,7 +20471,7 @@
         <v>0</v>
       </c>
       <c r="K119">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L119">
         <v>20</v>
@@ -20491,18 +20491,18 @@
         <v>パッシブ</v>
       </c>
       <c r="Q119">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R119" t="str">
         <f>INDEX(Define!K:K,MATCH(Q119,Define!J:J))</f>
-        <v>味方</v>
+        <v>追撃</v>
       </c>
       <c r="S119">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="T119" t="str">
         <f>INDEX(Define!N:N,MATCH(S119,Define!M:M))</f>
-        <v>単体・自身を除く</v>
+        <v>単体</v>
       </c>
       <c r="U119">
         <v>1</v>
@@ -20519,14 +20519,14 @@
     </row>
     <row r="120" spans="1:24">
       <c r="A120">
-        <v>13011</v>
+        <v>13030</v>
       </c>
       <c r="B120">
-        <v>13010</v>
+        <v>13030</v>
       </c>
       <c r="C120" t="str">
         <f>INDEX(TextData!B:B,MATCH(B120,TextData!A:A))</f>
-        <v>ヘビィカバー</v>
+        <v>カウンターマジック</v>
       </c>
       <c r="D120">
         <v>6</v>
@@ -20536,11 +20536,11 @@
         <v>自己強化</v>
       </c>
       <c r="F120">
-        <v>803</v>
+        <v>1109</v>
       </c>
       <c r="G120" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F120,[1]Animations!A:A))</f>
-        <v>MakerEffect/Powerup3</v>
+        <v>MakerEffect/Flash</v>
       </c>
       <c r="H120">
         <v>1</v>
@@ -20553,10 +20553,10 @@
         <v>0</v>
       </c>
       <c r="K120">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L120">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M120">
         <v>3</v>
@@ -20573,18 +20573,18 @@
         <v>パッシブ</v>
       </c>
       <c r="Q120">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R120" t="str">
         <f>INDEX(Define!K:K,MATCH(Q120,Define!J:J))</f>
-        <v>自身</v>
+        <v>反撃</v>
       </c>
       <c r="S120">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T120" t="str">
         <f>INDEX(Define!N:N,MATCH(S120,Define!M:M))</f>
-        <v>自身</v>
+        <v>単体</v>
       </c>
       <c r="U120">
         <v>1</v>
@@ -20601,14 +20601,14 @@
     </row>
     <row r="121" spans="1:24">
       <c r="A121">
-        <v>13020</v>
+        <v>13040</v>
       </c>
       <c r="B121">
-        <v>13020</v>
+        <v>13040</v>
       </c>
       <c r="C121" t="str">
         <f>INDEX(TextData!B:B,MATCH(B121,TextData!A:A))</f>
-        <v>アイシクルエッジ</v>
+        <v>アーマーコード</v>
       </c>
       <c r="D121">
         <v>6</v>
@@ -20618,11 +20618,11 @@
         <v>自己強化</v>
       </c>
       <c r="F121">
-        <v>1024</v>
+        <v>803</v>
       </c>
       <c r="G121" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F121,[1]Animations!A:A))</f>
-        <v>MakerEffect/PierceIce</v>
+        <v>MakerEffect/Powerup3</v>
       </c>
       <c r="H121">
         <v>1</v>
@@ -20655,18 +20655,18 @@
         <v>パッシブ</v>
       </c>
       <c r="Q121">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R121" t="str">
         <f>INDEX(Define!K:K,MATCH(Q121,Define!J:J))</f>
-        <v>追撃</v>
+        <v>自身</v>
       </c>
       <c r="S121">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T121" t="str">
         <f>INDEX(Define!N:N,MATCH(S121,Define!M:M))</f>
-        <v>単体</v>
+        <v>自身</v>
       </c>
       <c r="U121">
         <v>1</v>
@@ -20683,14 +20683,14 @@
     </row>
     <row r="122" spans="1:24">
       <c r="A122">
-        <v>13030</v>
+        <v>13050</v>
       </c>
       <c r="B122">
-        <v>13030</v>
+        <v>13050</v>
       </c>
       <c r="C122" t="str">
         <f>INDEX(TextData!B:B,MATCH(B122,TextData!A:A))</f>
-        <v>カウンターマジック</v>
+        <v>キュアフリーズ</v>
       </c>
       <c r="D122">
         <v>6</v>
@@ -20700,11 +20700,11 @@
         <v>自己強化</v>
       </c>
       <c r="F122">
-        <v>1109</v>
+        <v>3023</v>
       </c>
       <c r="G122" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F122,[1]Animations!A:A))</f>
-        <v>MakerEffect/Flash</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_Cure</v>
       </c>
       <c r="H122">
         <v>1</v>
@@ -20717,7 +20717,7 @@
         <v>0</v>
       </c>
       <c r="K122">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L122">
         <v>20</v>
@@ -20737,11 +20737,11 @@
         <v>パッシブ</v>
       </c>
       <c r="Q122">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R122" t="str">
         <f>INDEX(Define!K:K,MATCH(Q122,Define!J:J))</f>
-        <v>反撃</v>
+        <v>味方</v>
       </c>
       <c r="S122">
         <v>1</v>
@@ -20765,14 +20765,14 @@
     </row>
     <row r="123" spans="1:24">
       <c r="A123">
-        <v>13040</v>
+        <v>13070</v>
       </c>
       <c r="B123">
-        <v>13040</v>
+        <v>13070</v>
       </c>
       <c r="C123" t="str">
         <f>INDEX(TextData!B:B,MATCH(B123,TextData!A:A))</f>
-        <v>アーマーコード</v>
+        <v>アシッドラッシュ</v>
       </c>
       <c r="D123">
         <v>6</v>
@@ -20782,11 +20782,11 @@
         <v>自己強化</v>
       </c>
       <c r="F123">
-        <v>803</v>
+        <v>1024</v>
       </c>
       <c r="G123" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F123,[1]Animations!A:A))</f>
-        <v>MakerEffect/Powerup3</v>
+        <v>MakerEffect/PierceIce</v>
       </c>
       <c r="H123">
         <v>1</v>
@@ -20819,18 +20819,18 @@
         <v>パッシブ</v>
       </c>
       <c r="Q123">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R123" t="str">
         <f>INDEX(Define!K:K,MATCH(Q123,Define!J:J))</f>
-        <v>自身</v>
+        <v>追撃</v>
       </c>
       <c r="S123">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T123" t="str">
         <f>INDEX(Define!N:N,MATCH(S123,Define!M:M))</f>
-        <v>自身</v>
+        <v>単体</v>
       </c>
       <c r="U123">
         <v>1</v>
@@ -20847,14 +20847,14 @@
     </row>
     <row r="124" spans="1:24">
       <c r="A124">
-        <v>13050</v>
+        <v>13090</v>
       </c>
       <c r="B124">
-        <v>13050</v>
+        <v>13090</v>
       </c>
       <c r="C124" t="str">
         <f>INDEX(TextData!B:B,MATCH(B124,TextData!A:A))</f>
-        <v>キュアフリーズ</v>
+        <v>アイスセイバー</v>
       </c>
       <c r="D124">
         <v>6</v>
@@ -20864,11 +20864,11 @@
         <v>自己強化</v>
       </c>
       <c r="F124">
-        <v>3023</v>
+        <v>1024</v>
       </c>
       <c r="G124" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F124,[1]Animations!A:A))</f>
-        <v>Genfulew_Effect/B&amp;S_MinMax_Cure</v>
+        <v>MakerEffect/PierceIce</v>
       </c>
       <c r="H124">
         <v>1</v>
@@ -20881,7 +20881,7 @@
         <v>0</v>
       </c>
       <c r="K124">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L124">
         <v>20</v>
@@ -20901,18 +20901,18 @@
         <v>パッシブ</v>
       </c>
       <c r="Q124">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R124" t="str">
         <f>INDEX(Define!K:K,MATCH(Q124,Define!J:J))</f>
-        <v>味方</v>
+        <v>追撃</v>
       </c>
       <c r="S124">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T124" t="str">
         <f>INDEX(Define!N:N,MATCH(S124,Define!M:M))</f>
-        <v>単体</v>
+        <v>全体</v>
       </c>
       <c r="U124">
         <v>1</v>
@@ -20929,14 +20929,14 @@
     </row>
     <row r="125" spans="1:24">
       <c r="A125">
-        <v>13070</v>
+        <v>13110</v>
       </c>
       <c r="B125">
-        <v>13070</v>
+        <v>13110</v>
       </c>
       <c r="C125" t="str">
         <f>INDEX(TextData!B:B,MATCH(B125,TextData!A:A))</f>
-        <v>アシッドラッシュ</v>
+        <v>ガーディアン</v>
       </c>
       <c r="D125">
         <v>6</v>
@@ -20946,11 +20946,11 @@
         <v>自己強化</v>
       </c>
       <c r="F125">
-        <v>1024</v>
+        <v>803</v>
       </c>
       <c r="G125" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F125,[1]Animations!A:A))</f>
-        <v>MakerEffect/PierceIce</v>
+        <v>MakerEffect/Powerup3</v>
       </c>
       <c r="H125">
         <v>1</v>
@@ -20963,10 +20963,10 @@
         <v>0</v>
       </c>
       <c r="K125">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L125">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M125">
         <v>3</v>
@@ -20983,18 +20983,18 @@
         <v>パッシブ</v>
       </c>
       <c r="Q125">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R125" t="str">
         <f>INDEX(Define!K:K,MATCH(Q125,Define!J:J))</f>
-        <v>追撃</v>
+        <v>自身</v>
       </c>
       <c r="S125">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T125" t="str">
         <f>INDEX(Define!N:N,MATCH(S125,Define!M:M))</f>
-        <v>単体</v>
+        <v>自身</v>
       </c>
       <c r="U125">
         <v>1</v>
@@ -21011,14 +21011,14 @@
     </row>
     <row r="126" spans="1:24">
       <c r="A126">
-        <v>13090</v>
+        <v>13120</v>
       </c>
       <c r="B126">
-        <v>13090</v>
+        <v>13120</v>
       </c>
       <c r="C126" t="str">
         <f>INDEX(TextData!B:B,MATCH(B126,TextData!A:A))</f>
-        <v>アイスセイバー</v>
+        <v>ライフセーブ</v>
       </c>
       <c r="D126">
         <v>6</v>
@@ -21028,11 +21028,11 @@
         <v>自己強化</v>
       </c>
       <c r="F126">
-        <v>1024</v>
+        <v>803</v>
       </c>
       <c r="G126" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F126,[1]Animations!A:A))</f>
-        <v>MakerEffect/PierceIce</v>
+        <v>MakerEffect/Powerup3</v>
       </c>
       <c r="H126">
         <v>1</v>
@@ -21045,10 +21045,10 @@
         <v>0</v>
       </c>
       <c r="K126">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L126">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M126">
         <v>3</v>
@@ -21065,18 +21065,18 @@
         <v>パッシブ</v>
       </c>
       <c r="Q126">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R126" t="str">
         <f>INDEX(Define!K:K,MATCH(Q126,Define!J:J))</f>
-        <v>追撃</v>
+        <v>自身</v>
       </c>
       <c r="S126">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T126" t="str">
         <f>INDEX(Define!N:N,MATCH(S126,Define!M:M))</f>
-        <v>全体</v>
+        <v>自身</v>
       </c>
       <c r="U126">
         <v>1</v>
@@ -21093,14 +21093,14 @@
     </row>
     <row r="127" spans="1:24">
       <c r="A127">
-        <v>13110</v>
+        <v>13130</v>
       </c>
       <c r="B127">
-        <v>13110</v>
+        <v>13130</v>
       </c>
       <c r="C127" t="str">
         <f>INDEX(TextData!B:B,MATCH(B127,TextData!A:A))</f>
-        <v>ガーディアン</v>
+        <v>ライフスティール</v>
       </c>
       <c r="D127">
         <v>6</v>
@@ -21110,11 +21110,11 @@
         <v>自己強化</v>
       </c>
       <c r="F127">
-        <v>803</v>
+        <v>3347</v>
       </c>
       <c r="G127" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F127,[1]Animations!A:A))</f>
-        <v>MakerEffect/Powerup3</v>
+        <v>Genfulew_Effect/Enemy_CR_Charge2</v>
       </c>
       <c r="H127">
         <v>1</v>
@@ -21173,16 +21173,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:24">
+    <row r="128" ht="12" customHeight="1" spans="1:24">
       <c r="A128">
-        <v>13120</v>
+        <v>13140</v>
       </c>
       <c r="B128">
-        <v>13120</v>
+        <v>13140</v>
       </c>
       <c r="C128" t="str">
         <f>INDEX(TextData!B:B,MATCH(B128,TextData!A:A))</f>
-        <v>ライフセーブ</v>
+        <v>クイックバリア</v>
       </c>
       <c r="D128">
         <v>6</v>
@@ -21208,7 +21208,7 @@
       <c r="J128">
         <v>0</v>
       </c>
-      <c r="K128">
+      <c r="K128" s="7">
         <v>3</v>
       </c>
       <c r="L128">
@@ -21229,18 +21229,18 @@
         <v>パッシブ</v>
       </c>
       <c r="Q128">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="R128" t="str">
         <f>INDEX(Define!K:K,MATCH(Q128,Define!J:J))</f>
-        <v>自身</v>
+        <v>Triggerの条件を満たす</v>
       </c>
       <c r="S128">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T128" t="str">
         <f>INDEX(Define!N:N,MATCH(S128,Define!M:M))</f>
-        <v>自身</v>
+        <v>単体</v>
       </c>
       <c r="U128">
         <v>1</v>
@@ -21252,19 +21252,19 @@
         <v>1</v>
       </c>
       <c r="X128">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:24">
       <c r="A129">
-        <v>13130</v>
+        <v>13210</v>
       </c>
       <c r="B129">
-        <v>13130</v>
+        <v>13210</v>
       </c>
       <c r="C129" t="str">
         <f>INDEX(TextData!B:B,MATCH(B129,TextData!A:A))</f>
-        <v>ライフスティール</v>
+        <v>ルミナスカバー</v>
       </c>
       <c r="D129">
         <v>6</v>
@@ -21274,11 +21274,11 @@
         <v>自己強化</v>
       </c>
       <c r="F129">
-        <v>3347</v>
+        <v>1109</v>
       </c>
       <c r="G129" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F129,[1]Animations!A:A))</f>
-        <v>Genfulew_Effect/Enemy_CR_Charge2</v>
+        <v>MakerEffect/Flash</v>
       </c>
       <c r="H129">
         <v>1</v>
@@ -21311,18 +21311,18 @@
         <v>パッシブ</v>
       </c>
       <c r="Q129">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R129" t="str">
         <f>INDEX(Define!K:K,MATCH(Q129,Define!J:J))</f>
-        <v>自身</v>
+        <v>味方</v>
       </c>
       <c r="S129">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T129" t="str">
         <f>INDEX(Define!N:N,MATCH(S129,Define!M:M))</f>
-        <v>自身</v>
+        <v>単体・自身を除く</v>
       </c>
       <c r="U129">
         <v>1</v>
@@ -21339,7 +21339,7 @@
     </row>
     <row r="130" spans="1:24">
       <c r="A130">
-        <v>13210</v>
+        <v>13211</v>
       </c>
       <c r="B130">
         <v>13210</v>
@@ -21356,11 +21356,11 @@
         <v>自己強化</v>
       </c>
       <c r="F130">
-        <v>1109</v>
+        <v>803</v>
       </c>
       <c r="G130" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F130,[1]Animations!A:A))</f>
-        <v>MakerEffect/Flash</v>
+        <v>MakerEffect/Powerup3</v>
       </c>
       <c r="H130">
         <v>1</v>
@@ -21376,7 +21376,7 @@
         <v>3</v>
       </c>
       <c r="L130">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M130">
         <v>3</v>
@@ -21393,18 +21393,18 @@
         <v>パッシブ</v>
       </c>
       <c r="Q130">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R130" t="str">
         <f>INDEX(Define!K:K,MATCH(Q130,Define!J:J))</f>
-        <v>味方</v>
+        <v>自身</v>
       </c>
       <c r="S130">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T130" t="str">
         <f>INDEX(Define!N:N,MATCH(S130,Define!M:M))</f>
-        <v>単体・自身を除く</v>
+        <v>自身</v>
       </c>
       <c r="U130">
         <v>1</v>
@@ -21421,14 +21421,14 @@
     </row>
     <row r="131" spans="1:24">
       <c r="A131">
-        <v>13211</v>
+        <v>13510</v>
       </c>
       <c r="B131">
-        <v>13210</v>
+        <v>13510</v>
       </c>
       <c r="C131" t="str">
         <f>INDEX(TextData!B:B,MATCH(B131,TextData!A:A))</f>
-        <v>ルミナスカバー</v>
+        <v>デコイプラス</v>
       </c>
       <c r="D131">
         <v>6</v>
@@ -21438,11 +21438,11 @@
         <v>自己強化</v>
       </c>
       <c r="F131">
-        <v>803</v>
+        <v>1024</v>
       </c>
       <c r="G131" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F131,[1]Animations!A:A))</f>
-        <v>MakerEffect/Powerup3</v>
+        <v>MakerEffect/PierceIce</v>
       </c>
       <c r="H131">
         <v>1</v>
@@ -21458,7 +21458,7 @@
         <v>3</v>
       </c>
       <c r="L131">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M131">
         <v>3</v>
@@ -21475,18 +21475,18 @@
         <v>パッシブ</v>
       </c>
       <c r="Q131">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R131" t="str">
         <f>INDEX(Define!K:K,MATCH(Q131,Define!J:J))</f>
-        <v>自身</v>
+        <v>追撃</v>
       </c>
       <c r="S131">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T131" t="str">
         <f>INDEX(Define!N:N,MATCH(S131,Define!M:M))</f>
-        <v>自身</v>
+        <v>単体</v>
       </c>
       <c r="U131">
         <v>1</v>
@@ -21503,7 +21503,7 @@
     </row>
     <row r="132" spans="1:24">
       <c r="A132">
-        <v>13510</v>
+        <v>13511</v>
       </c>
       <c r="B132">
         <v>13510</v>
@@ -21520,11 +21520,11 @@
         <v>自己強化</v>
       </c>
       <c r="F132">
-        <v>1024</v>
+        <v>803</v>
       </c>
       <c r="G132" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F132,[1]Animations!A:A))</f>
-        <v>MakerEffect/PierceIce</v>
+        <v>MakerEffect/Powerup3</v>
       </c>
       <c r="H132">
         <v>1</v>
@@ -21540,7 +21540,7 @@
         <v>3</v>
       </c>
       <c r="L132">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M132">
         <v>3</v>
@@ -21557,18 +21557,18 @@
         <v>パッシブ</v>
       </c>
       <c r="Q132">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R132" t="str">
         <f>INDEX(Define!K:K,MATCH(Q132,Define!J:J))</f>
-        <v>追撃</v>
+        <v>自身</v>
       </c>
       <c r="S132">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T132" t="str">
         <f>INDEX(Define!N:N,MATCH(S132,Define!M:M))</f>
-        <v>単体</v>
+        <v>自身</v>
       </c>
       <c r="U132">
         <v>1</v>
@@ -21585,14 +21585,14 @@
     </row>
     <row r="133" spans="1:24">
       <c r="A133">
-        <v>13511</v>
+        <v>13520</v>
       </c>
       <c r="B133">
-        <v>13510</v>
+        <v>13520</v>
       </c>
       <c r="C133" t="str">
         <f>INDEX(TextData!B:B,MATCH(B133,TextData!A:A))</f>
-        <v>デコイプラス</v>
+        <v>アフターシールド</v>
       </c>
       <c r="D133">
         <v>6</v>
@@ -21622,7 +21622,7 @@
         <v>3</v>
       </c>
       <c r="L133">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M133">
         <v>3</v>
@@ -21667,14 +21667,14 @@
     </row>
     <row r="134" spans="1:24">
       <c r="A134">
-        <v>13520</v>
+        <v>13530</v>
       </c>
       <c r="B134">
-        <v>13520</v>
+        <v>13530</v>
       </c>
       <c r="C134" t="str">
         <f>INDEX(TextData!B:B,MATCH(B134,TextData!A:A))</f>
-        <v>アフターシールド</v>
+        <v>カバープラス</v>
       </c>
       <c r="D134">
         <v>6</v>
@@ -21747,16 +21747,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:24">
+    <row r="135" ht="12" customHeight="1" spans="1:24">
       <c r="A135">
-        <v>13530</v>
+        <v>13930</v>
       </c>
       <c r="B135">
-        <v>13530</v>
+        <v>13930</v>
       </c>
       <c r="C135" t="str">
         <f>INDEX(TextData!B:B,MATCH(B135,TextData!A:A))</f>
-        <v>カバープラス</v>
+        <v>クイックキュア</v>
       </c>
       <c r="D135">
         <v>6</v>
@@ -21766,11 +21766,11 @@
         <v>自己強化</v>
       </c>
       <c r="F135">
-        <v>803</v>
+        <v>3023</v>
       </c>
       <c r="G135" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F135,[1]Animations!A:A))</f>
-        <v>MakerEffect/Powerup3</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_Cure</v>
       </c>
       <c r="H135">
         <v>1</v>
@@ -21782,8 +21782,8 @@
       <c r="J135">
         <v>0</v>
       </c>
-      <c r="K135">
-        <v>3</v>
+      <c r="K135" s="7">
+        <v>2</v>
       </c>
       <c r="L135">
         <v>30</v>
@@ -21803,18 +21803,18 @@
         <v>パッシブ</v>
       </c>
       <c r="Q135">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="R135" t="str">
         <f>INDEX(Define!K:K,MATCH(Q135,Define!J:J))</f>
-        <v>自身</v>
+        <v>Triggerの条件を満たす</v>
       </c>
       <c r="S135">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T135" t="str">
         <f>INDEX(Define!N:N,MATCH(S135,Define!M:M))</f>
-        <v>自身</v>
+        <v>単体</v>
       </c>
       <c r="U135">
         <v>1</v>
@@ -21826,19 +21826,19 @@
         <v>1</v>
       </c>
       <c r="X135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" ht="12" customHeight="1" spans="1:24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:24">
       <c r="A136">
-        <v>13920</v>
+        <v>13940</v>
       </c>
       <c r="B136">
-        <v>13920</v>
+        <v>13940</v>
       </c>
       <c r="C136" t="str">
         <f>INDEX(TextData!B:B,MATCH(B136,TextData!A:A))</f>
-        <v>クイックバリア</v>
+        <v>セルフシールド</v>
       </c>
       <c r="D136">
         <v>6</v>
@@ -21864,7 +21864,7 @@
       <c r="J136">
         <v>0</v>
       </c>
-      <c r="K136" s="7">
+      <c r="K136">
         <v>3</v>
       </c>
       <c r="L136">
@@ -21885,18 +21885,18 @@
         <v>パッシブ</v>
       </c>
       <c r="Q136">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="R136" t="str">
         <f>INDEX(Define!K:K,MATCH(Q136,Define!J:J))</f>
-        <v>Triggerの条件を満たす</v>
+        <v>自身</v>
       </c>
       <c r="S136">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T136" t="str">
         <f>INDEX(Define!N:N,MATCH(S136,Define!M:M))</f>
-        <v>単体</v>
+        <v>自身</v>
       </c>
       <c r="U136">
         <v>1</v>
@@ -21908,19 +21908,19 @@
         <v>1</v>
       </c>
       <c r="X136">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="137" ht="12" customHeight="1" spans="1:24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:24">
       <c r="A137">
-        <v>13930</v>
+        <v>13950</v>
       </c>
       <c r="B137">
-        <v>13930</v>
+        <v>13950</v>
       </c>
       <c r="C137" t="str">
         <f>INDEX(TextData!B:B,MATCH(B137,TextData!A:A))</f>
-        <v>クイックキュア</v>
+        <v>パッシブジャミング</v>
       </c>
       <c r="D137">
         <v>6</v>
@@ -21930,11 +21930,11 @@
         <v>自己強化</v>
       </c>
       <c r="F137">
-        <v>3023</v>
+        <v>1109</v>
       </c>
       <c r="G137" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F137,[1]Animations!A:A))</f>
-        <v>Genfulew_Effect/B&amp;S_MinMax_Cure</v>
+        <v>MakerEffect/Flash</v>
       </c>
       <c r="H137">
         <v>1</v>
@@ -21946,11 +21946,11 @@
       <c r="J137">
         <v>0</v>
       </c>
-      <c r="K137" s="7">
-        <v>2</v>
+      <c r="K137">
+        <v>5</v>
       </c>
       <c r="L137">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M137">
         <v>3</v>
@@ -21993,16 +21993,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:24">
+    <row r="138" ht="12" customHeight="1" spans="1:24">
       <c r="A138">
-        <v>13940</v>
+        <v>14010</v>
       </c>
       <c r="B138">
-        <v>13940</v>
+        <v>14010</v>
       </c>
       <c r="C138" t="str">
         <f>INDEX(TextData!B:B,MATCH(B138,TextData!A:A))</f>
-        <v>セルフシールド</v>
+        <v>ファーストエイド</v>
       </c>
       <c r="D138">
         <v>6</v>
@@ -22012,11 +22012,11 @@
         <v>自己強化</v>
       </c>
       <c r="F138">
-        <v>803</v>
+        <v>3023</v>
       </c>
       <c r="G138" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F138,[1]Animations!A:A))</f>
-        <v>MakerEffect/Powerup3</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_Cure</v>
       </c>
       <c r="H138">
         <v>1</v>
@@ -22029,17 +22029,17 @@
         <v>0</v>
       </c>
       <c r="K138">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L138">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M138">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N138" t="str">
         <f>INDEX(Define!E:E,MATCH(M138,Define!D:D))</f>
-        <v>氷</v>
+        <v>光</v>
       </c>
       <c r="O138">
         <v>2</v>
@@ -22049,18 +22049,18 @@
         <v>パッシブ</v>
       </c>
       <c r="Q138">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="R138" t="str">
         <f>INDEX(Define!K:K,MATCH(Q138,Define!J:J))</f>
-        <v>自身</v>
+        <v>Triggerの条件を満たす</v>
       </c>
       <c r="S138">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T138" t="str">
         <f>INDEX(Define!N:N,MATCH(S138,Define!M:M))</f>
-        <v>自身</v>
+        <v>単体</v>
       </c>
       <c r="U138">
         <v>1</v>
@@ -22072,19 +22072,19 @@
         <v>1</v>
       </c>
       <c r="X138">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="1:24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" ht="12" customHeight="1" spans="1:24">
       <c r="A139">
-        <v>13950</v>
+        <v>14020</v>
       </c>
       <c r="B139">
-        <v>13950</v>
+        <v>14020</v>
       </c>
       <c r="C139" t="str">
         <f>INDEX(TextData!B:B,MATCH(B139,TextData!A:A))</f>
-        <v>パッシブジャミング</v>
+        <v>クイックヒール</v>
       </c>
       <c r="D139">
         <v>6</v>
@@ -22094,11 +22094,11 @@
         <v>自己強化</v>
       </c>
       <c r="F139">
-        <v>1109</v>
+        <v>3023</v>
       </c>
       <c r="G139" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F139,[1]Animations!A:A))</f>
-        <v>MakerEffect/Flash</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_Cure</v>
       </c>
       <c r="H139">
         <v>1</v>
@@ -22117,11 +22117,11 @@
         <v>20</v>
       </c>
       <c r="M139">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N139" t="str">
         <f>INDEX(Define!E:E,MATCH(M139,Define!D:D))</f>
-        <v>氷</v>
+        <v>光</v>
       </c>
       <c r="O139">
         <v>2</v>
@@ -22159,14 +22159,14 @@
     </row>
     <row r="140" ht="12" customHeight="1" spans="1:24">
       <c r="A140">
-        <v>14010</v>
+        <v>14030</v>
       </c>
       <c r="B140">
-        <v>14010</v>
+        <v>14030</v>
       </c>
       <c r="C140" t="str">
         <f>INDEX(TextData!B:B,MATCH(B140,TextData!A:A))</f>
-        <v>ファーストエイド</v>
+        <v>ガードバインド</v>
       </c>
       <c r="D140">
         <v>6</v>
@@ -22176,11 +22176,11 @@
         <v>自己強化</v>
       </c>
       <c r="F140">
-        <v>3023</v>
+        <v>1109</v>
       </c>
       <c r="G140" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F140,[1]Animations!A:A))</f>
-        <v>Genfulew_Effect/B&amp;S_MinMax_Cure</v>
+        <v>MakerEffect/Flash</v>
       </c>
       <c r="H140">
         <v>1</v>
@@ -22193,7 +22193,7 @@
         <v>0</v>
       </c>
       <c r="K140">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L140">
         <v>20</v>
@@ -22213,18 +22213,18 @@
         <v>パッシブ</v>
       </c>
       <c r="Q140">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="R140" t="str">
         <f>INDEX(Define!K:K,MATCH(Q140,Define!J:J))</f>
-        <v>Triggerの条件を満たす</v>
+        <v>自身</v>
       </c>
       <c r="S140">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T140" t="str">
         <f>INDEX(Define!N:N,MATCH(S140,Define!M:M))</f>
-        <v>単体</v>
+        <v>自身</v>
       </c>
       <c r="U140">
         <v>1</v>
@@ -22236,19 +22236,19 @@
         <v>1</v>
       </c>
       <c r="X140">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141" ht="12" customHeight="1" spans="1:24">
       <c r="A141">
-        <v>14020</v>
+        <v>14040</v>
       </c>
       <c r="B141">
-        <v>14020</v>
+        <v>14040</v>
       </c>
       <c r="C141" t="str">
         <f>INDEX(TextData!B:B,MATCH(B141,TextData!A:A))</f>
-        <v>クイックヒール</v>
+        <v>ホープフルアイリス</v>
       </c>
       <c r="D141">
         <v>6</v>
@@ -22258,11 +22258,11 @@
         <v>自己強化</v>
       </c>
       <c r="F141">
-        <v>3023</v>
+        <v>1109</v>
       </c>
       <c r="G141" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F141,[1]Animations!A:A))</f>
-        <v>Genfulew_Effect/B&amp;S_MinMax_Cure</v>
+        <v>MakerEffect/Flash</v>
       </c>
       <c r="H141">
         <v>1</v>
@@ -22275,7 +22275,7 @@
         <v>0</v>
       </c>
       <c r="K141">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L141">
         <v>20</v>
@@ -22295,18 +22295,18 @@
         <v>パッシブ</v>
       </c>
       <c r="Q141">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="R141" t="str">
         <f>INDEX(Define!K:K,MATCH(Q141,Define!J:J))</f>
-        <v>Triggerの条件を満たす</v>
+        <v>自身</v>
       </c>
       <c r="S141">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T141" t="str">
         <f>INDEX(Define!N:N,MATCH(S141,Define!M:M))</f>
-        <v>単体</v>
+        <v>自身</v>
       </c>
       <c r="U141">
         <v>1</v>
@@ -22318,19 +22318,19 @@
         <v>1</v>
       </c>
       <c r="X141">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" ht="12" customHeight="1" spans="1:24">
       <c r="A142">
-        <v>14030</v>
+        <v>14050</v>
       </c>
       <c r="B142">
-        <v>14030</v>
+        <v>14050</v>
       </c>
       <c r="C142" t="str">
         <f>INDEX(TextData!B:B,MATCH(B142,TextData!A:A))</f>
-        <v>ガードバインド</v>
+        <v>キュアパッシブ</v>
       </c>
       <c r="D142">
         <v>6</v>
@@ -22340,11 +22340,11 @@
         <v>自己強化</v>
       </c>
       <c r="F142">
-        <v>1109</v>
+        <v>3023</v>
       </c>
       <c r="G142" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F142,[1]Animations!A:A))</f>
-        <v>MakerEffect/Flash</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_Cure</v>
       </c>
       <c r="H142">
         <v>1</v>
@@ -22357,7 +22357,7 @@
         <v>0</v>
       </c>
       <c r="K142">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L142">
         <v>20</v>
@@ -22377,18 +22377,18 @@
         <v>パッシブ</v>
       </c>
       <c r="Q142">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R142" t="str">
         <f>INDEX(Define!K:K,MATCH(Q142,Define!J:J))</f>
-        <v>自身</v>
+        <v>味方</v>
       </c>
       <c r="S142">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T142" t="str">
         <f>INDEX(Define!N:N,MATCH(S142,Define!M:M))</f>
-        <v>自身</v>
+        <v>単体</v>
       </c>
       <c r="U142">
         <v>1</v>
@@ -22405,14 +22405,14 @@
     </row>
     <row r="143" ht="12" customHeight="1" spans="1:24">
       <c r="A143">
-        <v>14040</v>
+        <v>14060</v>
       </c>
       <c r="B143">
-        <v>14040</v>
+        <v>14060</v>
       </c>
       <c r="C143" t="str">
         <f>INDEX(TextData!B:B,MATCH(B143,TextData!A:A))</f>
-        <v>ホープフルアイリス</v>
+        <v>パッシブサプライ</v>
       </c>
       <c r="D143">
         <v>6</v>
@@ -22459,18 +22459,18 @@
         <v>パッシブ</v>
       </c>
       <c r="Q143">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R143" t="str">
         <f>INDEX(Define!K:K,MATCH(Q143,Define!J:J))</f>
-        <v>自身</v>
+        <v>反撃</v>
       </c>
       <c r="S143">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T143" t="str">
         <f>INDEX(Define!N:N,MATCH(S143,Define!M:M))</f>
-        <v>自身</v>
+        <v>単体</v>
       </c>
       <c r="U143">
         <v>1</v>
@@ -22487,14 +22487,14 @@
     </row>
     <row r="144" ht="12" customHeight="1" spans="1:24">
       <c r="A144">
-        <v>14050</v>
+        <v>14070</v>
       </c>
       <c r="B144">
-        <v>14050</v>
+        <v>14070</v>
       </c>
       <c r="C144" t="str">
         <f>INDEX(TextData!B:B,MATCH(B144,TextData!A:A))</f>
-        <v>キュアパッシブ</v>
+        <v>ホーミングクルセイド</v>
       </c>
       <c r="D144">
         <v>6</v>
@@ -22504,11 +22504,11 @@
         <v>自己強化</v>
       </c>
       <c r="F144">
-        <v>3023</v>
+        <v>1109</v>
       </c>
       <c r="G144" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F144,[1]Animations!A:A))</f>
-        <v>Genfulew_Effect/B&amp;S_MinMax_Cure</v>
+        <v>MakerEffect/Flash</v>
       </c>
       <c r="H144">
         <v>1</v>
@@ -22541,18 +22541,18 @@
         <v>パッシブ</v>
       </c>
       <c r="Q144">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R144" t="str">
         <f>INDEX(Define!K:K,MATCH(Q144,Define!J:J))</f>
-        <v>味方</v>
+        <v>自身</v>
       </c>
       <c r="S144">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T144" t="str">
         <f>INDEX(Define!N:N,MATCH(S144,Define!M:M))</f>
-        <v>単体</v>
+        <v>自身</v>
       </c>
       <c r="U144">
         <v>1</v>
@@ -22569,14 +22569,14 @@
     </row>
     <row r="145" ht="12" customHeight="1" spans="1:24">
       <c r="A145">
-        <v>14060</v>
+        <v>14090</v>
       </c>
       <c r="B145">
-        <v>14060</v>
+        <v>14090</v>
       </c>
       <c r="C145" t="str">
         <f>INDEX(TextData!B:B,MATCH(B145,TextData!A:A))</f>
-        <v>パッシブサプライ</v>
+        <v>リレイズ</v>
       </c>
       <c r="D145">
         <v>6</v>
@@ -22586,11 +22586,11 @@
         <v>自己強化</v>
       </c>
       <c r="F145">
-        <v>1109</v>
+        <v>3027</v>
       </c>
       <c r="G145" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F145,[1]Animations!A:A))</f>
-        <v>MakerEffect/Flash</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_Regeneration1</v>
       </c>
       <c r="H145">
         <v>1</v>
@@ -22603,7 +22603,7 @@
         <v>0</v>
       </c>
       <c r="K145">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L145">
         <v>20</v>
@@ -22623,18 +22623,18 @@
         <v>パッシブ</v>
       </c>
       <c r="Q145">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R145" t="str">
         <f>INDEX(Define!K:K,MATCH(Q145,Define!J:J))</f>
-        <v>反撃</v>
+        <v>自身</v>
       </c>
       <c r="S145">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T145" t="str">
         <f>INDEX(Define!N:N,MATCH(S145,Define!M:M))</f>
-        <v>単体</v>
+        <v>自身</v>
       </c>
       <c r="U145">
         <v>1</v>
@@ -22651,14 +22651,14 @@
     </row>
     <row r="146" ht="12" customHeight="1" spans="1:24">
       <c r="A146">
-        <v>14070</v>
+        <v>14100</v>
       </c>
       <c r="B146">
-        <v>14070</v>
+        <v>14100</v>
       </c>
       <c r="C146" t="str">
         <f>INDEX(TextData!B:B,MATCH(B146,TextData!A:A))</f>
-        <v>ホーミングクルセイド</v>
+        <v>ファストヒール</v>
       </c>
       <c r="D146">
         <v>6</v>
@@ -22668,11 +22668,11 @@
         <v>自己強化</v>
       </c>
       <c r="F146">
-        <v>1109</v>
+        <v>3023</v>
       </c>
       <c r="G146" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F146,[1]Animations!A:A))</f>
-        <v>MakerEffect/Flash</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_Cure</v>
       </c>
       <c r="H146">
         <v>1</v>
@@ -22705,21 +22705,21 @@
         <v>パッシブ</v>
       </c>
       <c r="Q146">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R146" t="str">
         <f>INDEX(Define!K:K,MATCH(Q146,Define!J:J))</f>
-        <v>自身</v>
+        <v>味方</v>
       </c>
       <c r="S146">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T146" t="str">
         <f>INDEX(Define!N:N,MATCH(S146,Define!M:M))</f>
-        <v>自身</v>
+        <v>全体</v>
       </c>
       <c r="U146">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V146">
         <v>1</v>
@@ -22733,14 +22733,14 @@
     </row>
     <row r="147" ht="12" customHeight="1" spans="1:24">
       <c r="A147">
-        <v>14090</v>
+        <v>14110</v>
       </c>
       <c r="B147">
-        <v>14090</v>
+        <v>14110</v>
       </c>
       <c r="C147" t="str">
         <f>INDEX(TextData!B:B,MATCH(B147,TextData!A:A))</f>
-        <v>リレイズ</v>
+        <v>リフレッシュ</v>
       </c>
       <c r="D147">
         <v>6</v>
@@ -22750,11 +22750,11 @@
         <v>自己強化</v>
       </c>
       <c r="F147">
-        <v>3027</v>
+        <v>3023</v>
       </c>
       <c r="G147" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F147,[1]Animations!A:A))</f>
-        <v>Genfulew_Effect/B&amp;S_MinMax_Regeneration1</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_Cure</v>
       </c>
       <c r="H147">
         <v>1</v>
@@ -22767,10 +22767,10 @@
         <v>0</v>
       </c>
       <c r="K147">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L147">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M147">
         <v>4</v>
@@ -22787,18 +22787,18 @@
         <v>パッシブ</v>
       </c>
       <c r="Q147">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R147" t="str">
         <f>INDEX(Define!K:K,MATCH(Q147,Define!J:J))</f>
-        <v>自身</v>
+        <v>味方</v>
       </c>
       <c r="S147">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T147" t="str">
         <f>INDEX(Define!N:N,MATCH(S147,Define!M:M))</f>
-        <v>自身</v>
+        <v>単体</v>
       </c>
       <c r="U147">
         <v>1</v>
@@ -22815,14 +22815,14 @@
     </row>
     <row r="148" ht="12" customHeight="1" spans="1:24">
       <c r="A148">
-        <v>14100</v>
+        <v>14120</v>
       </c>
       <c r="B148">
-        <v>14100</v>
+        <v>14120</v>
       </c>
       <c r="C148" t="str">
         <f>INDEX(TextData!B:B,MATCH(B148,TextData!A:A))</f>
-        <v>ファストヒール</v>
+        <v>ファストメディック</v>
       </c>
       <c r="D148">
         <v>6</v>
@@ -22849,10 +22849,10 @@
         <v>0</v>
       </c>
       <c r="K148">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L148">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M148">
         <v>4</v>
@@ -22876,14 +22876,14 @@
         <v>味方</v>
       </c>
       <c r="S148">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T148" t="str">
         <f>INDEX(Define!N:N,MATCH(S148,Define!M:M))</f>
-        <v>全体</v>
+        <v>列</v>
       </c>
       <c r="U148">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V148">
         <v>1</v>
@@ -22897,14 +22897,14 @@
     </row>
     <row r="149" ht="12" customHeight="1" spans="1:24">
       <c r="A149">
-        <v>14110</v>
+        <v>14130</v>
       </c>
       <c r="B149">
-        <v>14110</v>
+        <v>14130</v>
       </c>
       <c r="C149" t="str">
         <f>INDEX(TextData!B:B,MATCH(B149,TextData!A:A))</f>
-        <v>リフレッシュ</v>
+        <v>ディバインシールド</v>
       </c>
       <c r="D149">
         <v>6</v>
@@ -22914,11 +22914,11 @@
         <v>自己強化</v>
       </c>
       <c r="F149">
-        <v>3023</v>
+        <v>1109</v>
       </c>
       <c r="G149" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F149,[1]Animations!A:A))</f>
-        <v>Genfulew_Effect/B&amp;S_MinMax_Cure</v>
+        <v>MakerEffect/Flash</v>
       </c>
       <c r="H149">
         <v>1</v>
@@ -22931,7 +22931,7 @@
         <v>0</v>
       </c>
       <c r="K149">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L149">
         <v>30</v>
@@ -22951,18 +22951,18 @@
         <v>パッシブ</v>
       </c>
       <c r="Q149">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R149" t="str">
         <f>INDEX(Define!K:K,MATCH(Q149,Define!J:J))</f>
-        <v>味方</v>
+        <v>自身</v>
       </c>
       <c r="S149">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T149" t="str">
         <f>INDEX(Define!N:N,MATCH(S149,Define!M:M))</f>
-        <v>単体</v>
+        <v>自身</v>
       </c>
       <c r="U149">
         <v>1</v>
@@ -22979,14 +22979,14 @@
     </row>
     <row r="150" ht="12" customHeight="1" spans="1:24">
       <c r="A150">
-        <v>14120</v>
+        <v>14140</v>
       </c>
       <c r="B150">
-        <v>14120</v>
+        <v>14140</v>
       </c>
       <c r="C150" t="str">
         <f>INDEX(TextData!B:B,MATCH(B150,TextData!A:A))</f>
-        <v>ファストメディック</v>
+        <v>ライフディバイド</v>
       </c>
       <c r="D150">
         <v>6</v>
@@ -23033,18 +23033,18 @@
         <v>パッシブ</v>
       </c>
       <c r="Q150">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="R150" t="str">
         <f>INDEX(Define!K:K,MATCH(Q150,Define!J:J))</f>
-        <v>味方</v>
+        <v>Triggerの条件を満たす</v>
       </c>
       <c r="S150">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T150" t="str">
         <f>INDEX(Define!N:N,MATCH(S150,Define!M:M))</f>
-        <v>列</v>
+        <v>単体</v>
       </c>
       <c r="U150">
         <v>1</v>
@@ -23056,19 +23056,19 @@
         <v>1</v>
       </c>
       <c r="X150">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151" ht="12" customHeight="1" spans="1:24">
       <c r="A151">
-        <v>14130</v>
+        <v>14930</v>
       </c>
       <c r="B151">
-        <v>14130</v>
+        <v>14930</v>
       </c>
       <c r="C151" t="str">
         <f>INDEX(TextData!B:B,MATCH(B151,TextData!A:A))</f>
-        <v>ディバインシールド</v>
+        <v>エイミングスコープ</v>
       </c>
       <c r="D151">
         <v>6</v>
@@ -23115,18 +23115,18 @@
         <v>パッシブ</v>
       </c>
       <c r="Q151">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R151" t="str">
         <f>INDEX(Define!K:K,MATCH(Q151,Define!J:J))</f>
-        <v>自身</v>
+        <v>味方</v>
       </c>
       <c r="S151">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T151" t="str">
         <f>INDEX(Define!N:N,MATCH(S151,Define!M:M))</f>
-        <v>自身</v>
+        <v>全体</v>
       </c>
       <c r="U151">
         <v>1</v>
@@ -23143,14 +23143,14 @@
     </row>
     <row r="152" ht="12" customHeight="1" spans="1:24">
       <c r="A152">
-        <v>14920</v>
+        <v>14940</v>
       </c>
       <c r="B152">
-        <v>14920</v>
+        <v>14940</v>
       </c>
       <c r="C152" t="str">
         <f>INDEX(TextData!B:B,MATCH(B152,TextData!A:A))</f>
-        <v>ライフディバイド</v>
+        <v>リジェネレーション</v>
       </c>
       <c r="D152">
         <v>6</v>
@@ -23197,18 +23197,18 @@
         <v>パッシブ</v>
       </c>
       <c r="Q152">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="R152" t="str">
         <f>INDEX(Define!K:K,MATCH(Q152,Define!J:J))</f>
-        <v>Triggerの条件を満たす</v>
+        <v>自身</v>
       </c>
       <c r="S152">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T152" t="str">
         <f>INDEX(Define!N:N,MATCH(S152,Define!M:M))</f>
-        <v>単体</v>
+        <v>自身</v>
       </c>
       <c r="U152">
         <v>1</v>
@@ -23220,19 +23220,19 @@
         <v>1</v>
       </c>
       <c r="X152">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="153" ht="12" customHeight="1" spans="1:24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:24">
       <c r="A153">
-        <v>14930</v>
+        <v>15010</v>
       </c>
       <c r="B153">
-        <v>14930</v>
+        <v>15010</v>
       </c>
       <c r="C153" t="str">
         <f>INDEX(TextData!B:B,MATCH(B153,TextData!A:A))</f>
-        <v>エイミングスコープ</v>
+        <v>ワンスパニッシュ</v>
       </c>
       <c r="D153">
         <v>6</v>
@@ -23262,14 +23262,14 @@
         <v>0</v>
       </c>
       <c r="L153">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M153">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N153" t="str">
         <f>INDEX(Define!E:E,MATCH(M153,Define!D:D))</f>
-        <v>光</v>
+        <v>闇</v>
       </c>
       <c r="O153">
         <v>2</v>
@@ -23279,18 +23279,18 @@
         <v>パッシブ</v>
       </c>
       <c r="Q153">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R153" t="str">
         <f>INDEX(Define!K:K,MATCH(Q153,Define!J:J))</f>
-        <v>味方</v>
+        <v>自身</v>
       </c>
       <c r="S153">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T153" t="str">
         <f>INDEX(Define!N:N,MATCH(S153,Define!M:M))</f>
-        <v>全体</v>
+        <v>自身</v>
       </c>
       <c r="U153">
         <v>1</v>
@@ -23307,14 +23307,14 @@
     </row>
     <row r="154" ht="12" customHeight="1" spans="1:24">
       <c r="A154">
-        <v>14940</v>
+        <v>15020</v>
       </c>
       <c r="B154">
-        <v>14940</v>
+        <v>15020</v>
       </c>
       <c r="C154" t="str">
         <f>INDEX(TextData!B:B,MATCH(B154,TextData!A:A))</f>
-        <v>リジェネレーション</v>
+        <v>クイックカース</v>
       </c>
       <c r="D154">
         <v>6</v>
@@ -23324,11 +23324,11 @@
         <v>自己強化</v>
       </c>
       <c r="F154">
-        <v>3023</v>
+        <v>3047</v>
       </c>
       <c r="G154" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F154,[1]Animations!A:A))</f>
-        <v>Genfulew_Effect/B&amp;S_MinMax_Cure</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_Dispel</v>
       </c>
       <c r="H154">
         <v>1</v>
@@ -23344,14 +23344,14 @@
         <v>3</v>
       </c>
       <c r="L154">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M154">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N154" t="str">
         <f>INDEX(Define!E:E,MATCH(M154,Define!D:D))</f>
-        <v>光</v>
+        <v>闇</v>
       </c>
       <c r="O154">
         <v>2</v>
@@ -23361,21 +23361,21 @@
         <v>パッシブ</v>
       </c>
       <c r="Q154">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R154" t="str">
         <f>INDEX(Define!K:K,MATCH(Q154,Define!J:J))</f>
-        <v>自身</v>
+        <v>反撃</v>
       </c>
       <c r="S154">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T154" t="str">
         <f>INDEX(Define!N:N,MATCH(S154,Define!M:M))</f>
-        <v>自身</v>
+        <v>単体</v>
       </c>
       <c r="U154">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V154">
         <v>1</v>
@@ -23384,19 +23384,19 @@
         <v>1</v>
       </c>
       <c r="X154">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="1:24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" ht="12" customHeight="1" spans="1:24">
       <c r="A155">
-        <v>15010</v>
+        <v>15030</v>
       </c>
       <c r="B155">
-        <v>15010</v>
+        <v>15030</v>
       </c>
       <c r="C155" t="str">
         <f>INDEX(TextData!B:B,MATCH(B155,TextData!A:A))</f>
-        <v>ワンスパニッシュ</v>
+        <v>バイタリティ</v>
       </c>
       <c r="D155">
         <v>6</v>
@@ -23423,7 +23423,7 @@
         <v>0</v>
       </c>
       <c r="K155">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L155">
         <v>20</v>
@@ -23471,14 +23471,14 @@
     </row>
     <row r="156" ht="12" customHeight="1" spans="1:24">
       <c r="A156">
-        <v>15020</v>
+        <v>15040</v>
       </c>
       <c r="B156">
-        <v>15020</v>
+        <v>15040</v>
       </c>
       <c r="C156" t="str">
         <f>INDEX(TextData!B:B,MATCH(B156,TextData!A:A))</f>
-        <v>クイックカース</v>
+        <v>ネガティブドレイン</v>
       </c>
       <c r="D156">
         <v>6</v>
@@ -23488,11 +23488,11 @@
         <v>自己強化</v>
       </c>
       <c r="F156">
-        <v>3047</v>
+        <v>3302</v>
       </c>
       <c r="G156" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F156,[1]Animations!A:A))</f>
-        <v>Genfulew_Effect/B&amp;S_MinMax_Dispel</v>
+        <v>Genfulew_Effect/Enemy_CR_ActivationMagic</v>
       </c>
       <c r="H156">
         <v>1</v>
@@ -23505,7 +23505,7 @@
         <v>0</v>
       </c>
       <c r="K156">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L156">
         <v>20</v>
@@ -23525,21 +23525,21 @@
         <v>パッシブ</v>
       </c>
       <c r="Q156">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R156" t="str">
         <f>INDEX(Define!K:K,MATCH(Q156,Define!J:J))</f>
-        <v>反撃</v>
+        <v>自身</v>
       </c>
       <c r="S156">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T156" t="str">
         <f>INDEX(Define!N:N,MATCH(S156,Define!M:M))</f>
-        <v>単体</v>
+        <v>自身</v>
       </c>
       <c r="U156">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V156">
         <v>1</v>
@@ -23548,19 +23548,19 @@
         <v>1</v>
       </c>
       <c r="X156">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157" ht="12" customHeight="1" spans="1:24">
       <c r="A157">
-        <v>15030</v>
+        <v>15050</v>
       </c>
       <c r="B157">
-        <v>15030</v>
+        <v>15050</v>
       </c>
       <c r="C157" t="str">
         <f>INDEX(TextData!B:B,MATCH(B157,TextData!A:A))</f>
-        <v>バイタリティ</v>
+        <v>キュアシェイド</v>
       </c>
       <c r="D157">
         <v>6</v>
@@ -23570,11 +23570,11 @@
         <v>自己強化</v>
       </c>
       <c r="F157">
-        <v>1109</v>
+        <v>3023</v>
       </c>
       <c r="G157" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F157,[1]Animations!A:A))</f>
-        <v>MakerEffect/Flash</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_Cure</v>
       </c>
       <c r="H157">
         <v>1</v>
@@ -23587,7 +23587,7 @@
         <v>0</v>
       </c>
       <c r="K157">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L157">
         <v>20</v>
@@ -23607,18 +23607,18 @@
         <v>パッシブ</v>
       </c>
       <c r="Q157">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R157" t="str">
         <f>INDEX(Define!K:K,MATCH(Q157,Define!J:J))</f>
-        <v>自身</v>
+        <v>味方</v>
       </c>
       <c r="S157">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T157" t="str">
         <f>INDEX(Define!N:N,MATCH(S157,Define!M:M))</f>
-        <v>自身</v>
+        <v>単体</v>
       </c>
       <c r="U157">
         <v>1</v>
@@ -23635,14 +23635,14 @@
     </row>
     <row r="158" ht="12" customHeight="1" spans="1:24">
       <c r="A158">
-        <v>15040</v>
+        <v>15060</v>
       </c>
       <c r="B158">
-        <v>15040</v>
+        <v>15060</v>
       </c>
       <c r="C158" t="str">
         <f>INDEX(TextData!B:B,MATCH(B158,TextData!A:A))</f>
-        <v>ネガティブドレイン</v>
+        <v>アンデッドペイン</v>
       </c>
       <c r="D158">
         <v>6</v>
@@ -23652,11 +23652,11 @@
         <v>自己強化</v>
       </c>
       <c r="F158">
-        <v>3302</v>
+        <v>3047</v>
       </c>
       <c r="G158" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F158,[1]Animations!A:A))</f>
-        <v>Genfulew_Effect/Enemy_CR_ActivationMagic</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_Dispel</v>
       </c>
       <c r="H158">
         <v>1</v>
@@ -23717,14 +23717,14 @@
     </row>
     <row r="159" ht="12" customHeight="1" spans="1:24">
       <c r="A159">
-        <v>15050</v>
+        <v>15070</v>
       </c>
       <c r="B159">
-        <v>15050</v>
+        <v>15070</v>
       </c>
       <c r="C159" t="str">
         <f>INDEX(TextData!B:B,MATCH(B159,TextData!A:A))</f>
-        <v>キュアシェイド</v>
+        <v>ジャックポッド</v>
       </c>
       <c r="D159">
         <v>6</v>
@@ -23734,11 +23734,11 @@
         <v>自己強化</v>
       </c>
       <c r="F159">
-        <v>3023</v>
+        <v>3047</v>
       </c>
       <c r="G159" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F159,[1]Animations!A:A))</f>
-        <v>Genfulew_Effect/B&amp;S_MinMax_Cure</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_Dispel</v>
       </c>
       <c r="H159">
         <v>1</v>
@@ -23751,7 +23751,7 @@
         <v>0</v>
       </c>
       <c r="K159">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L159">
         <v>20</v>
@@ -23771,11 +23771,11 @@
         <v>パッシブ</v>
       </c>
       <c r="Q159">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="R159" t="str">
         <f>INDEX(Define!K:K,MATCH(Q159,Define!J:J))</f>
-        <v>味方</v>
+        <v>Triggerの条件を満たす</v>
       </c>
       <c r="S159">
         <v>1</v>
@@ -23794,19 +23794,19 @@
         <v>1</v>
       </c>
       <c r="X159">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160" ht="12" customHeight="1" spans="1:24">
       <c r="A160">
-        <v>15060</v>
+        <v>15080</v>
       </c>
       <c r="B160">
-        <v>15060</v>
+        <v>15080</v>
       </c>
       <c r="C160" t="str">
         <f>INDEX(TextData!B:B,MATCH(B160,TextData!A:A))</f>
-        <v>アンデッドペイン</v>
+        <v>ヒールハント</v>
       </c>
       <c r="D160">
         <v>6</v>
@@ -23833,7 +23833,7 @@
         <v>0</v>
       </c>
       <c r="K160">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L160">
         <v>20</v>
@@ -23853,21 +23853,21 @@
         <v>パッシブ</v>
       </c>
       <c r="Q160">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R160" t="str">
         <f>INDEX(Define!K:K,MATCH(Q160,Define!J:J))</f>
-        <v>自身</v>
+        <v>反撃</v>
       </c>
       <c r="S160">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T160" t="str">
         <f>INDEX(Define!N:N,MATCH(S160,Define!M:M))</f>
-        <v>自身</v>
+        <v>単体</v>
       </c>
       <c r="U160">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V160">
         <v>1</v>
@@ -23881,14 +23881,14 @@
     </row>
     <row r="161" ht="12" customHeight="1" spans="1:24">
       <c r="A161">
-        <v>15070</v>
+        <v>15110</v>
       </c>
       <c r="B161">
-        <v>15070</v>
+        <v>15110</v>
       </c>
       <c r="C161" t="str">
         <f>INDEX(TextData!B:B,MATCH(B161,TextData!A:A))</f>
-        <v>ジャックポッド</v>
+        <v>フォーカサイト</v>
       </c>
       <c r="D161">
         <v>6</v>
@@ -23898,11 +23898,11 @@
         <v>自己強化</v>
       </c>
       <c r="F161">
-        <v>3047</v>
+        <v>3302</v>
       </c>
       <c r="G161" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F161,[1]Animations!A:A))</f>
-        <v>Genfulew_Effect/B&amp;S_MinMax_Dispel</v>
+        <v>Genfulew_Effect/Enemy_CR_ActivationMagic</v>
       </c>
       <c r="H161">
         <v>1</v>
@@ -23918,7 +23918,7 @@
         <v>3</v>
       </c>
       <c r="L161">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M161">
         <v>5</v>
@@ -23935,11 +23935,11 @@
         <v>パッシブ</v>
       </c>
       <c r="Q161">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="R161" t="str">
         <f>INDEX(Define!K:K,MATCH(Q161,Define!J:J))</f>
-        <v>Triggerの条件を満たす</v>
+        <v>味方</v>
       </c>
       <c r="S161">
         <v>1</v>
@@ -23958,19 +23958,19 @@
         <v>1</v>
       </c>
       <c r="X161">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162" ht="12" customHeight="1" spans="1:24">
       <c r="A162">
-        <v>15080</v>
+        <v>15120</v>
       </c>
       <c r="B162">
-        <v>15080</v>
+        <v>15120</v>
       </c>
       <c r="C162" t="str">
         <f>INDEX(TextData!B:B,MATCH(B162,TextData!A:A))</f>
-        <v>ヒールハント</v>
+        <v>ガードハント</v>
       </c>
       <c r="D162">
         <v>6</v>
@@ -23997,10 +23997,10 @@
         <v>0</v>
       </c>
       <c r="K162">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L162">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M162">
         <v>5</v>
@@ -24045,14 +24045,14 @@
     </row>
     <row r="163" ht="12" customHeight="1" spans="1:24">
       <c r="A163">
-        <v>15110</v>
+        <v>15130</v>
       </c>
       <c r="B163">
-        <v>15110</v>
+        <v>15130</v>
       </c>
       <c r="C163" t="str">
         <f>INDEX(TextData!B:B,MATCH(B163,TextData!A:A))</f>
-        <v>フォーカサイト</v>
+        <v>リヴェンジャー</v>
       </c>
       <c r="D163">
         <v>6</v>
@@ -24099,18 +24099,18 @@
         <v>パッシブ</v>
       </c>
       <c r="Q163">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R163" t="str">
         <f>INDEX(Define!K:K,MATCH(Q163,Define!J:J))</f>
-        <v>味方</v>
+        <v>自身</v>
       </c>
       <c r="S163">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T163" t="str">
         <f>INDEX(Define!N:N,MATCH(S163,Define!M:M))</f>
-        <v>単体</v>
+        <v>自身</v>
       </c>
       <c r="U163">
         <v>1</v>
@@ -24125,16 +24125,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" ht="12" customHeight="1" spans="1:24">
+    <row r="164" spans="1:24">
       <c r="A164">
-        <v>15120</v>
+        <v>15140</v>
       </c>
       <c r="B164">
-        <v>15120</v>
+        <v>15140</v>
       </c>
       <c r="C164" t="str">
         <f>INDEX(TextData!B:B,MATCH(B164,TextData!A:A))</f>
-        <v>ガードハント</v>
+        <v>ソーサリーコネクト</v>
       </c>
       <c r="D164">
         <v>6</v>
@@ -24144,11 +24144,11 @@
         <v>自己強化</v>
       </c>
       <c r="F164">
-        <v>3047</v>
+        <v>3005</v>
       </c>
       <c r="G164" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F164,[1]Animations!A:A))</f>
-        <v>Genfulew_Effect/B&amp;S_MinMax_Dispel</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_AttackUp</v>
       </c>
       <c r="H164">
         <v>1</v>
@@ -24161,7 +24161,7 @@
         <v>0</v>
       </c>
       <c r="K164">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L164">
         <v>30</v>
@@ -24181,11 +24181,11 @@
         <v>パッシブ</v>
       </c>
       <c r="Q164">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="R164" t="str">
         <f>INDEX(Define!K:K,MATCH(Q164,Define!J:J))</f>
-        <v>反撃</v>
+        <v>Triggerの条件を満たす</v>
       </c>
       <c r="S164">
         <v>1</v>
@@ -24195,7 +24195,7 @@
         <v>単体</v>
       </c>
       <c r="U164">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V164">
         <v>1</v>
@@ -24204,19 +24204,19 @@
         <v>1</v>
       </c>
       <c r="X164">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165" ht="12" customHeight="1" spans="1:24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:24">
       <c r="A165">
-        <v>15130</v>
+        <v>15141</v>
       </c>
       <c r="B165">
-        <v>15130</v>
+        <v>15140</v>
       </c>
       <c r="C165" t="str">
         <f>INDEX(TextData!B:B,MATCH(B165,TextData!A:A))</f>
-        <v>リヴェンジャー</v>
+        <v>ソーサリーコネクト</v>
       </c>
       <c r="D165">
         <v>6</v>
@@ -24226,11 +24226,11 @@
         <v>自己強化</v>
       </c>
       <c r="F165">
-        <v>3302</v>
+        <v>3006</v>
       </c>
       <c r="G165" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F165,[1]Animations!A:A))</f>
-        <v>Genfulew_Effect/Enemy_CR_ActivationMagic</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_AttackDown</v>
       </c>
       <c r="H165">
         <v>1</v>
@@ -24243,10 +24243,10 @@
         <v>0</v>
       </c>
       <c r="K165">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L165">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M165">
         <v>5</v>
@@ -47443,57 +47443,54 @@
         <v>100</v>
       </c>
     </row>
-    <row r="139" spans="1:9">
+    <row r="139" spans="1:8">
       <c r="A139">
-        <v>12070</v>
+        <v>12090</v>
       </c>
       <c r="B139" t="str">
         <f>INDEX(TextData!B:B,MATCH(A139,TextData!A:A))</f>
-        <v>ソーサリーコネクト</v>
+        <v>アウトオブオーダー</v>
       </c>
       <c r="C139">
-        <v>3010</v>
+        <v>5020</v>
       </c>
       <c r="D139" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C139,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Ap回復</v>
       </c>
       <c r="E139">
-        <v>1040</v>
+        <v>200</v>
       </c>
       <c r="F139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G139">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H139">
         <v>100</v>
       </c>
-      <c r="I139" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8">
+    </row>
+    <row r="140" spans="1:9">
       <c r="A140">
-        <v>12070</v>
+        <v>12100</v>
       </c>
       <c r="B140" t="str">
         <f>INDEX(TextData!B:B,MATCH(A140,TextData!A:A))</f>
-        <v>ソーサリーコネクト</v>
+        <v>ワンスパニッシュ</v>
       </c>
       <c r="C140">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D140" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C140,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E140">
-        <v>12071</v>
+        <v>2050</v>
       </c>
       <c r="F140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G140">
         <v>0</v>
@@ -47501,73 +47498,79 @@
       <c r="H140">
         <v>100</v>
       </c>
+      <c r="I140" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="141" spans="1:9">
       <c r="A141">
-        <v>12071</v>
+        <v>12110</v>
       </c>
       <c r="B141" t="str">
         <f>INDEX(TextData!B:B,MATCH(A141,TextData!A:A))</f>
-        <v>ソーサリーコネクト</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="C141">
-        <v>3010</v>
+        <v>3040</v>
       </c>
       <c r="D141" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C141,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>次の行動まで有効なステート付与</v>
       </c>
       <c r="E141">
-        <v>1041</v>
+        <v>1080</v>
       </c>
       <c r="F141">
         <v>1</v>
       </c>
       <c r="G141">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H141">
         <v>100</v>
       </c>
       <c r="I141" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9">
       <c r="A142">
-        <v>12090</v>
+        <v>12110</v>
       </c>
       <c r="B142" t="str">
         <f>INDEX(TextData!B:B,MATCH(A142,TextData!A:A))</f>
-        <v>アウトオブオーダー</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="C142">
-        <v>5020</v>
+        <v>3040</v>
       </c>
       <c r="D142" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C142,Define!P:P))</f>
-        <v>Ap回復</v>
+        <v>次の行動まで有効なステート付与</v>
       </c>
       <c r="E142">
-        <v>200</v>
+        <v>1090</v>
       </c>
       <c r="F142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G142">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H142">
         <v>100</v>
       </c>
+      <c r="I142" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="143" spans="1:9">
       <c r="A143">
-        <v>12100</v>
+        <v>12120</v>
       </c>
       <c r="B143" t="str">
         <f>INDEX(TextData!B:B,MATCH(A143,TextData!A:A))</f>
-        <v>ワンスパニッシュ</v>
+        <v>パリィ</v>
       </c>
       <c r="C143">
         <v>3010</v>
@@ -47592,88 +47595,82 @@
         <v>33</v>
       </c>
     </row>
-    <row r="144" spans="1:9">
+    <row r="144" spans="1:8">
       <c r="A144">
-        <v>12110</v>
+        <v>12130</v>
       </c>
       <c r="B144" t="str">
         <f>INDEX(TextData!B:B,MATCH(A144,TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>チェイスマジック</v>
       </c>
       <c r="C144">
-        <v>3040</v>
+        <v>1010</v>
       </c>
       <c r="D144" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C144,Define!P:P))</f>
-        <v>次の行動まで有効なステート付与</v>
+        <v>Hpダメージ</v>
       </c>
       <c r="E144">
-        <v>1080</v>
+        <v>100</v>
       </c>
       <c r="F144">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G144">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H144">
         <v>100</v>
       </c>
-      <c r="I144" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="145" spans="1:9">
+    </row>
+    <row r="145" spans="1:8">
       <c r="A145">
-        <v>12110</v>
+        <v>12140</v>
       </c>
       <c r="B145" t="str">
         <f>INDEX(TextData!B:B,MATCH(A145,TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>ウィンドライズ</v>
       </c>
       <c r="C145">
-        <v>3040</v>
+        <v>1010</v>
       </c>
       <c r="D145" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C145,Define!P:P))</f>
-        <v>次の行動まで有効なステート付与</v>
+        <v>Hpダメージ</v>
       </c>
       <c r="E145">
-        <v>1090</v>
+        <v>100</v>
       </c>
       <c r="F145">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G145">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H145">
         <v>100</v>
       </c>
-      <c r="I145" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="146" spans="1:9">
+    </row>
+    <row r="146" spans="1:8">
       <c r="A146">
-        <v>12120</v>
+        <v>12510</v>
       </c>
       <c r="B146" t="str">
         <f>INDEX(TextData!B:B,MATCH(A146,TextData!A:A))</f>
-        <v>パリィ</v>
+        <v>アクトスタンス</v>
       </c>
       <c r="C146">
-        <v>3010</v>
+        <v>5020</v>
       </c>
       <c r="D146" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C146,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Ap回復</v>
       </c>
       <c r="E146">
-        <v>2050</v>
+        <v>200</v>
       </c>
       <c r="F146">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G146">
         <v>0</v>
@@ -47681,101 +47678,107 @@
       <c r="H146">
         <v>100</v>
       </c>
-      <c r="I146" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8">
+    </row>
+    <row r="147" spans="1:9">
       <c r="A147">
-        <v>12130</v>
+        <v>12510</v>
       </c>
       <c r="B147" t="str">
         <f>INDEX(TextData!B:B,MATCH(A147,TextData!A:A))</f>
-        <v>チェイスマジック</v>
+        <v>アクトスタンス</v>
       </c>
       <c r="C147">
-        <v>1010</v>
+        <v>3010</v>
       </c>
       <c r="D147" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C147,Define!P:P))</f>
-        <v>Hpダメージ</v>
+        <v>ステート付与</v>
       </c>
       <c r="E147">
-        <v>100</v>
+        <v>1041</v>
       </c>
       <c r="F147">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G147">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H147">
         <v>100</v>
       </c>
-    </row>
-    <row r="148" spans="1:8">
+      <c r="I147" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9">
       <c r="A148">
-        <v>12140</v>
+        <v>12910</v>
       </c>
       <c r="B148" t="str">
         <f>INDEX(TextData!B:B,MATCH(A148,TextData!A:A))</f>
-        <v>ウィンドライズ</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="C148">
-        <v>1010</v>
+        <v>3010</v>
       </c>
       <c r="D148" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C148,Define!P:P))</f>
-        <v>Hpダメージ</v>
+        <v>ステート付与</v>
       </c>
       <c r="E148">
-        <v>100</v>
+        <v>1080</v>
       </c>
       <c r="F148">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G148">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H148">
         <v>100</v>
       </c>
-    </row>
-    <row r="149" spans="1:8">
+      <c r="I148" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9">
       <c r="A149">
-        <v>12510</v>
+        <v>12910</v>
       </c>
       <c r="B149" t="str">
         <f>INDEX(TextData!B:B,MATCH(A149,TextData!A:A))</f>
-        <v>アクトスタンス</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="C149">
-        <v>5020</v>
+        <v>3010</v>
       </c>
       <c r="D149" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C149,Define!P:P))</f>
-        <v>Ap回復</v>
+        <v>ステート付与</v>
       </c>
       <c r="E149">
-        <v>200</v>
+        <v>1090</v>
       </c>
       <c r="F149">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G149">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H149">
         <v>100</v>
       </c>
+      <c r="I149" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="150" spans="1:9">
       <c r="A150">
-        <v>12510</v>
+        <v>12930</v>
       </c>
       <c r="B150" t="str">
         <f>INDEX(TextData!B:B,MATCH(A150,TextData!A:A))</f>
-        <v>アクトスタンス</v>
+        <v>スウィフトカレント</v>
       </c>
       <c r="C150">
         <v>3010</v>
@@ -47785,28 +47788,28 @@
         <v>ステート付与</v>
       </c>
       <c r="E150">
-        <v>1041</v>
+        <v>1060</v>
       </c>
       <c r="F150">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="G150">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H150">
         <v>100</v>
       </c>
       <c r="I150" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
     </row>
     <row r="151" spans="1:9">
       <c r="A151">
-        <v>12910</v>
+        <v>12940</v>
       </c>
       <c r="B151" t="str">
         <f>INDEX(TextData!B:B,MATCH(A151,TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>イヴェイドオール</v>
       </c>
       <c r="C151">
         <v>3010</v>
@@ -47816,28 +47819,28 @@
         <v>ステート付与</v>
       </c>
       <c r="E151">
-        <v>1080</v>
+        <v>1092</v>
       </c>
       <c r="F151">
         <v>999</v>
       </c>
       <c r="G151">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H151">
         <v>100</v>
       </c>
       <c r="I151" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="152" spans="1:9">
       <c r="A152">
-        <v>12910</v>
+        <v>13010</v>
       </c>
       <c r="B152" t="str">
         <f>INDEX(TextData!B:B,MATCH(A152,TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>ヘビィカバー</v>
       </c>
       <c r="C152">
         <v>3010</v>
@@ -47847,59 +47850,56 @@
         <v>ステート付与</v>
       </c>
       <c r="E152">
-        <v>1090</v>
+        <v>2430</v>
       </c>
       <c r="F152">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="G152">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H152">
         <v>100</v>
       </c>
       <c r="I152" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="153" spans="1:9">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8">
       <c r="A153">
-        <v>12930</v>
+        <v>13010</v>
       </c>
       <c r="B153" t="str">
         <f>INDEX(TextData!B:B,MATCH(A153,TextData!A:A))</f>
-        <v>スウィフトカレント</v>
+        <v>ヘビィカバー</v>
       </c>
       <c r="C153">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D153" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C153,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E153">
-        <v>1060</v>
+        <v>13011</v>
       </c>
       <c r="F153">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G153">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H153">
         <v>100</v>
       </c>
-      <c r="I153" t="s">
-        <v>52</v>
-      </c>
     </row>
     <row r="154" spans="1:9">
       <c r="A154">
-        <v>12940</v>
+        <v>13011</v>
       </c>
       <c r="B154" t="str">
         <f>INDEX(TextData!B:B,MATCH(A154,TextData!A:A))</f>
-        <v>イヴェイドオール</v>
+        <v>ヘビィカバー</v>
       </c>
       <c r="C154">
         <v>3010</v>
@@ -47909,28 +47909,28 @@
         <v>ステート付与</v>
       </c>
       <c r="E154">
-        <v>1092</v>
+        <v>1100</v>
       </c>
       <c r="F154">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="G154">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="H154">
         <v>100</v>
       </c>
       <c r="I154" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="155" spans="1:9">
       <c r="A155">
-        <v>13010</v>
+        <v>13020</v>
       </c>
       <c r="B155" t="str">
         <f>INDEX(TextData!B:B,MATCH(A155,TextData!A:A))</f>
-        <v>ヘビィカバー</v>
+        <v>アイシクルエッジ</v>
       </c>
       <c r="C155">
         <v>3010</v>
@@ -47940,44 +47940,44 @@
         <v>ステート付与</v>
       </c>
       <c r="E155">
-        <v>2430</v>
+        <v>2140</v>
       </c>
       <c r="F155">
         <v>1</v>
       </c>
       <c r="G155">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H155">
         <v>100</v>
       </c>
       <c r="I155" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
     </row>
     <row r="156" spans="1:8">
       <c r="A156">
-        <v>13010</v>
+        <v>13030</v>
       </c>
       <c r="B156" t="str">
         <f>INDEX(TextData!B:B,MATCH(A156,TextData!A:A))</f>
-        <v>ヘビィカバー</v>
+        <v>カウンターマジック</v>
       </c>
       <c r="C156">
-        <v>7010</v>
+        <v>1010</v>
       </c>
       <c r="D156" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C156,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>Hpダメージ</v>
       </c>
       <c r="E156">
-        <v>13011</v>
+        <v>100</v>
       </c>
       <c r="F156">
         <v>0</v>
       </c>
       <c r="G156">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H156">
         <v>100</v>
@@ -47985,11 +47985,11 @@
     </row>
     <row r="157" spans="1:9">
       <c r="A157">
-        <v>13011</v>
+        <v>13040</v>
       </c>
       <c r="B157" t="str">
         <f>INDEX(TextData!B:B,MATCH(A157,TextData!A:A))</f>
-        <v>ヘビィカバー</v>
+        <v>アーマーコード</v>
       </c>
       <c r="C157">
         <v>3010</v>
@@ -47999,187 +47999,187 @@
         <v>ステート付与</v>
       </c>
       <c r="E157">
-        <v>1100</v>
+        <v>1050</v>
       </c>
       <c r="F157">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="G157">
-        <v>75</v>
+        <v>2</v>
       </c>
       <c r="H157">
         <v>100</v>
       </c>
       <c r="I157" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="158" spans="1:9">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8">
       <c r="A158">
-        <v>13020</v>
+        <v>13050</v>
       </c>
       <c r="B158" t="str">
         <f>INDEX(TextData!B:B,MATCH(A158,TextData!A:A))</f>
-        <v>アイシクルエッジ</v>
+        <v>キュアフリーズ</v>
       </c>
       <c r="C158">
-        <v>3010</v>
+        <v>3020</v>
       </c>
       <c r="D158" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C158,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>ステート解除</v>
       </c>
       <c r="E158">
         <v>2140</v>
       </c>
       <c r="F158">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G158">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H158">
         <v>100</v>
       </c>
-      <c r="I158" t="s">
-        <v>31</v>
-      </c>
     </row>
     <row r="159" spans="1:8">
       <c r="A159">
-        <v>13030</v>
+        <v>13050</v>
       </c>
       <c r="B159" t="str">
         <f>INDEX(TextData!B:B,MATCH(A159,TextData!A:A))</f>
-        <v>カウンターマジック</v>
+        <v>キュアフリーズ</v>
       </c>
       <c r="C159">
-        <v>1010</v>
+        <v>2010</v>
       </c>
       <c r="D159" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C159,Define!P:P))</f>
-        <v>Hpダメージ</v>
+        <v>Hp回復</v>
       </c>
       <c r="E159">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F159">
         <v>0</v>
       </c>
       <c r="G159">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H159">
         <v>100</v>
       </c>
     </row>
-    <row r="160" spans="1:9">
+    <row r="160" spans="1:8">
       <c r="A160">
-        <v>13040</v>
+        <v>13070</v>
       </c>
       <c r="B160" t="str">
         <f>INDEX(TextData!B:B,MATCH(A160,TextData!A:A))</f>
-        <v>アーマーコード</v>
+        <v>アシッドラッシュ</v>
       </c>
       <c r="C160">
-        <v>3010</v>
+        <v>5050</v>
       </c>
       <c r="D160" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C160,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>APダメージ</v>
       </c>
       <c r="E160">
-        <v>1050</v>
+        <v>100</v>
       </c>
       <c r="F160">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G160">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H160">
         <v>100</v>
       </c>
-      <c r="I160" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="161" spans="1:8">
+    </row>
+    <row r="161" spans="1:9">
       <c r="A161">
-        <v>13050</v>
+        <v>13090</v>
       </c>
       <c r="B161" t="str">
         <f>INDEX(TextData!B:B,MATCH(A161,TextData!A:A))</f>
-        <v>キュアフリーズ</v>
+        <v>アイスセイバー</v>
       </c>
       <c r="C161">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="D161" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C161,Define!P:P))</f>
-        <v>ステート解除</v>
+        <v>ステート付与</v>
       </c>
       <c r="E161">
         <v>2140</v>
       </c>
       <c r="F161">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G161">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H161">
         <v>100</v>
       </c>
-    </row>
-    <row r="162" spans="1:8">
+      <c r="I161" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9">
       <c r="A162">
-        <v>13050</v>
+        <v>13110</v>
       </c>
       <c r="B162" t="str">
         <f>INDEX(TextData!B:B,MATCH(A162,TextData!A:A))</f>
-        <v>キュアフリーズ</v>
+        <v>ガーディアン</v>
       </c>
       <c r="C162">
-        <v>2010</v>
+        <v>3010</v>
       </c>
       <c r="D162" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C162,Define!P:P))</f>
-        <v>Hp回復</v>
+        <v>ステート付与</v>
       </c>
       <c r="E162">
-        <v>10</v>
+        <v>1052</v>
       </c>
       <c r="F162">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G162">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H162">
         <v>100</v>
       </c>
-    </row>
-    <row r="163" spans="1:8">
+      <c r="I162" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9">
       <c r="A163">
-        <v>13070</v>
+        <v>13120</v>
       </c>
       <c r="B163" t="str">
         <f>INDEX(TextData!B:B,MATCH(A163,TextData!A:A))</f>
-        <v>アシッドラッシュ</v>
+        <v>ライフセーブ</v>
       </c>
       <c r="C163">
-        <v>5050</v>
+        <v>3010</v>
       </c>
       <c r="D163" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C163,Define!P:P))</f>
-        <v>APダメージ</v>
+        <v>ステート付与</v>
       </c>
       <c r="E163">
-        <v>100</v>
+        <v>2450</v>
       </c>
       <c r="F163">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G163">
         <v>0</v>
@@ -48187,14 +48187,17 @@
       <c r="H163">
         <v>100</v>
       </c>
+      <c r="I163" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="164" spans="1:9">
       <c r="A164">
-        <v>13090</v>
+        <v>13130</v>
       </c>
       <c r="B164" t="str">
         <f>INDEX(TextData!B:B,MATCH(A164,TextData!A:A))</f>
-        <v>アイスセイバー</v>
+        <v>ライフスティール</v>
       </c>
       <c r="C164">
         <v>3010</v>
@@ -48204,7 +48207,7 @@
         <v>ステート付与</v>
       </c>
       <c r="E164">
-        <v>2140</v>
+        <v>2060</v>
       </c>
       <c r="F164">
         <v>1</v>
@@ -48216,16 +48219,16 @@
         <v>100</v>
       </c>
       <c r="I164" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
     </row>
     <row r="165" spans="1:9">
       <c r="A165">
-        <v>13110</v>
+        <v>13140</v>
       </c>
       <c r="B165" t="str">
         <f>INDEX(TextData!B:B,MATCH(A165,TextData!A:A))</f>
-        <v>ガーディアン</v>
+        <v>クイックバリア</v>
       </c>
       <c r="C165">
         <v>3010</v>
@@ -48235,28 +48238,28 @@
         <v>ステート付与</v>
       </c>
       <c r="E165">
-        <v>1052</v>
+        <v>1100</v>
       </c>
       <c r="F165">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G165">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H165">
         <v>100</v>
       </c>
       <c r="I165" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="166" spans="1:9">
       <c r="A166">
-        <v>13120</v>
+        <v>13210</v>
       </c>
       <c r="B166" t="str">
         <f>INDEX(TextData!B:B,MATCH(A166,TextData!A:A))</f>
-        <v>ライフセーブ</v>
+        <v>ルミナスカバー</v>
       </c>
       <c r="C166">
         <v>3010</v>
@@ -48266,7 +48269,7 @@
         <v>ステート付与</v>
       </c>
       <c r="E166">
-        <v>2450</v>
+        <v>2430</v>
       </c>
       <c r="F166">
         <v>1</v>
@@ -48278,43 +48281,40 @@
         <v>100</v>
       </c>
       <c r="I166" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="167" spans="1:9">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8">
       <c r="A167">
-        <v>13130</v>
+        <v>13210</v>
       </c>
       <c r="B167" t="str">
         <f>INDEX(TextData!B:B,MATCH(A167,TextData!A:A))</f>
-        <v>ライフスティール</v>
+        <v>ルミナスカバー</v>
       </c>
       <c r="C167">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D167" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C167,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E167">
-        <v>2060</v>
+        <v>13211</v>
       </c>
       <c r="F167">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G167">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H167">
         <v>100</v>
       </c>
-      <c r="I167" t="s">
-        <v>54</v>
-      </c>
     </row>
     <row r="168" spans="1:9">
       <c r="A168">
-        <v>13210</v>
+        <v>13211</v>
       </c>
       <c r="B168" t="str">
         <f>INDEX(TextData!B:B,MATCH(A168,TextData!A:A))</f>
@@ -48328,83 +48328,83 @@
         <v>ステート付与</v>
       </c>
       <c r="E168">
-        <v>2430</v>
+        <v>1100</v>
       </c>
       <c r="F168">
         <v>1</v>
       </c>
       <c r="G168">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H168">
         <v>100</v>
       </c>
       <c r="I168" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="169" spans="1:8">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9">
       <c r="A169">
-        <v>13210</v>
+        <v>13510</v>
       </c>
       <c r="B169" t="str">
         <f>INDEX(TextData!B:B,MATCH(A169,TextData!A:A))</f>
-        <v>ルミナスカバー</v>
+        <v>デコイプラス</v>
       </c>
       <c r="C169">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D169" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C169,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E169">
-        <v>13211</v>
+        <v>2130</v>
       </c>
       <c r="F169">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G169">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="H169">
         <v>100</v>
       </c>
-    </row>
-    <row r="170" spans="1:9">
+      <c r="I169" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8">
       <c r="A170">
-        <v>13211</v>
+        <v>13510</v>
       </c>
       <c r="B170" t="str">
         <f>INDEX(TextData!B:B,MATCH(A170,TextData!A:A))</f>
-        <v>ルミナスカバー</v>
+        <v>デコイプラス</v>
       </c>
       <c r="C170">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D170" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C170,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E170">
-        <v>1100</v>
+        <v>13111</v>
       </c>
       <c r="F170">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G170">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H170">
         <v>100</v>
       </c>
-      <c r="I170" t="s">
-        <v>40</v>
-      </c>
     </row>
     <row r="171" spans="1:9">
       <c r="A171">
-        <v>13510</v>
+        <v>13511</v>
       </c>
       <c r="B171" t="str">
         <f>INDEX(TextData!B:B,MATCH(A171,TextData!A:A))</f>
@@ -48418,56 +48418,59 @@
         <v>ステート付与</v>
       </c>
       <c r="E171">
-        <v>2130</v>
+        <v>1050</v>
       </c>
       <c r="F171">
         <v>1</v>
       </c>
       <c r="G171">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="H171">
         <v>100</v>
       </c>
       <c r="I171" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="172" spans="1:8">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9">
       <c r="A172">
-        <v>13510</v>
+        <v>13520</v>
       </c>
       <c r="B172" t="str">
         <f>INDEX(TextData!B:B,MATCH(A172,TextData!A:A))</f>
-        <v>デコイプラス</v>
+        <v>アフターシールド</v>
       </c>
       <c r="C172">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D172" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C172,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E172">
-        <v>13111</v>
+        <v>1052</v>
       </c>
       <c r="F172">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G172">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H172">
         <v>100</v>
       </c>
+      <c r="I172" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="173" spans="1:9">
       <c r="A173">
-        <v>13511</v>
+        <v>13530</v>
       </c>
       <c r="B173" t="str">
         <f>INDEX(TextData!B:B,MATCH(A173,TextData!A:A))</f>
-        <v>デコイプラス</v>
+        <v>カバープラス</v>
       </c>
       <c r="C173">
         <v>3010</v>
@@ -48477,59 +48480,56 @@
         <v>ステート付与</v>
       </c>
       <c r="E173">
-        <v>1050</v>
+        <v>1100</v>
       </c>
       <c r="F173">
         <v>1</v>
       </c>
       <c r="G173">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H173">
         <v>100</v>
       </c>
       <c r="I173" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="174" spans="1:9">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8">
       <c r="A174">
-        <v>13520</v>
+        <v>13930</v>
       </c>
       <c r="B174" t="str">
         <f>INDEX(TextData!B:B,MATCH(A174,TextData!A:A))</f>
-        <v>アフターシールド</v>
+        <v>クイックキュア</v>
       </c>
       <c r="C174">
-        <v>3010</v>
+        <v>3030</v>
       </c>
       <c r="D174" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C174,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Abnormalステート解除</v>
       </c>
       <c r="E174">
-        <v>1052</v>
+        <v>0</v>
       </c>
       <c r="F174">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G174">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H174">
         <v>100</v>
       </c>
-      <c r="I174" t="s">
-        <v>37</v>
-      </c>
     </row>
     <row r="175" spans="1:9">
       <c r="A175">
-        <v>13530</v>
+        <v>13940</v>
       </c>
       <c r="B175" t="str">
         <f>INDEX(TextData!B:B,MATCH(A175,TextData!A:A))</f>
-        <v>カバープラス</v>
+        <v>セルフシールド</v>
       </c>
       <c r="C175">
         <v>3010</v>
@@ -48556,11 +48556,11 @@
     </row>
     <row r="176" spans="1:9">
       <c r="A176">
-        <v>13920</v>
+        <v>13950</v>
       </c>
       <c r="B176" t="str">
         <f>INDEX(TextData!B:B,MATCH(A176,TextData!A:A))</f>
-        <v>クイックバリア</v>
+        <v>パッシブジャミング</v>
       </c>
       <c r="C176">
         <v>3010</v>
@@ -48570,38 +48570,38 @@
         <v>ステート付与</v>
       </c>
       <c r="E176">
-        <v>1100</v>
+        <v>2090</v>
       </c>
       <c r="F176">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G176">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H176">
         <v>100</v>
       </c>
       <c r="I176" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="177" spans="1:8">
       <c r="A177">
-        <v>13930</v>
+        <v>14010</v>
       </c>
       <c r="B177" t="str">
         <f>INDEX(TextData!B:B,MATCH(A177,TextData!A:A))</f>
-        <v>クイックキュア</v>
+        <v>ファーストエイド</v>
       </c>
       <c r="C177">
-        <v>3030</v>
+        <v>2010</v>
       </c>
       <c r="D177" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C177,Define!P:P))</f>
-        <v>Abnormalステート解除</v>
+        <v>Hp回復</v>
       </c>
       <c r="E177">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F177">
         <v>0</v>
@@ -48613,44 +48613,41 @@
         <v>100</v>
       </c>
     </row>
-    <row r="178" spans="1:9">
+    <row r="178" spans="1:8">
       <c r="A178">
-        <v>13940</v>
+        <v>14020</v>
       </c>
       <c r="B178" t="str">
         <f>INDEX(TextData!B:B,MATCH(A178,TextData!A:A))</f>
-        <v>セルフシールド</v>
+        <v>クイックヒール</v>
       </c>
       <c r="C178">
-        <v>3010</v>
+        <v>2010</v>
       </c>
       <c r="D178" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C178,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Hp回復</v>
       </c>
       <c r="E178">
-        <v>1100</v>
+        <v>5</v>
       </c>
       <c r="F178">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G178">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H178">
         <v>100</v>
       </c>
-      <c r="I178" t="s">
-        <v>40</v>
-      </c>
     </row>
     <row r="179" spans="1:9">
       <c r="A179">
-        <v>13950</v>
+        <v>14030</v>
       </c>
       <c r="B179" t="str">
         <f>INDEX(TextData!B:B,MATCH(A179,TextData!A:A))</f>
-        <v>パッシブジャミング</v>
+        <v>ガードバインド</v>
       </c>
       <c r="C179">
         <v>3010</v>
@@ -48660,66 +48657,69 @@
         <v>ステート付与</v>
       </c>
       <c r="E179">
-        <v>2090</v>
+        <v>2500</v>
       </c>
       <c r="F179">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G179">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H179">
         <v>100</v>
       </c>
       <c r="I179" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="180" spans="1:8">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9">
       <c r="A180">
-        <v>14010</v>
+        <v>14040</v>
       </c>
       <c r="B180" t="str">
         <f>INDEX(TextData!B:B,MATCH(A180,TextData!A:A))</f>
-        <v>ファーストエイド</v>
+        <v>ホープフルアイリス</v>
       </c>
       <c r="C180">
-        <v>2010</v>
+        <v>3010</v>
       </c>
       <c r="D180" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C180,Define!P:P))</f>
-        <v>Hp回復</v>
+        <v>ステート付与</v>
       </c>
       <c r="E180">
+        <v>1020</v>
+      </c>
+      <c r="F180">
+        <v>999</v>
+      </c>
+      <c r="G180">
         <v>5</v>
-      </c>
-      <c r="F180">
-        <v>0</v>
-      </c>
-      <c r="G180">
-        <v>0</v>
       </c>
       <c r="H180">
         <v>100</v>
       </c>
+      <c r="I180" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="181" spans="1:8">
       <c r="A181">
-        <v>14020</v>
+        <v>14050</v>
       </c>
       <c r="B181" t="str">
         <f>INDEX(TextData!B:B,MATCH(A181,TextData!A:A))</f>
-        <v>クイックヒール</v>
+        <v>キュアパッシブ</v>
       </c>
       <c r="C181">
-        <v>2010</v>
+        <v>3020</v>
       </c>
       <c r="D181" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C181,Define!P:P))</f>
-        <v>Hp回復</v>
+        <v>ステート解除</v>
       </c>
       <c r="E181">
-        <v>5</v>
+        <v>2090</v>
       </c>
       <c r="F181">
         <v>0</v>
@@ -48731,88 +48731,82 @@
         <v>100</v>
       </c>
     </row>
-    <row r="182" spans="1:9">
+    <row r="182" spans="1:8">
       <c r="A182">
-        <v>14030</v>
+        <v>14050</v>
       </c>
       <c r="B182" t="str">
         <f>INDEX(TextData!B:B,MATCH(A182,TextData!A:A))</f>
-        <v>ガードバインド</v>
+        <v>キュアパッシブ</v>
       </c>
       <c r="C182">
-        <v>3010</v>
+        <v>2010</v>
       </c>
       <c r="D182" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C182,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Hp回復</v>
       </c>
       <c r="E182">
-        <v>2500</v>
+        <v>10</v>
       </c>
       <c r="F182">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G182">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="H182">
         <v>100</v>
       </c>
-      <c r="I182" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="183" spans="1:9">
+    </row>
+    <row r="183" spans="1:8">
       <c r="A183">
-        <v>14040</v>
+        <v>14060</v>
       </c>
       <c r="B183" t="str">
         <f>INDEX(TextData!B:B,MATCH(A183,TextData!A:A))</f>
-        <v>ホープフルアイリス</v>
+        <v>パッシブサプライ</v>
       </c>
       <c r="C183">
-        <v>3010</v>
+        <v>4020</v>
       </c>
       <c r="D183" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C183,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Ct回復</v>
       </c>
       <c r="E183">
-        <v>1020</v>
+        <v>1</v>
       </c>
       <c r="F183">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G183">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H183">
         <v>100</v>
       </c>
-      <c r="I183" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="184" spans="1:8">
+    </row>
+    <row r="184" spans="1:9">
       <c r="A184">
-        <v>14050</v>
+        <v>14070</v>
       </c>
       <c r="B184" t="str">
         <f>INDEX(TextData!B:B,MATCH(A184,TextData!A:A))</f>
-        <v>キュアパッシブ</v>
+        <v>ホーミングクルセイド</v>
       </c>
       <c r="C184">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="D184" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C184,Define!P:P))</f>
-        <v>ステート解除</v>
+        <v>ステート付与</v>
       </c>
       <c r="E184">
-        <v>2090</v>
+        <v>2240</v>
       </c>
       <c r="F184">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G184">
         <v>0</v>
@@ -48820,27 +48814,30 @@
       <c r="H184">
         <v>100</v>
       </c>
-    </row>
-    <row r="185" spans="1:8">
+      <c r="I184" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9">
       <c r="A185">
-        <v>14050</v>
+        <v>14090</v>
       </c>
       <c r="B185" t="str">
         <f>INDEX(TextData!B:B,MATCH(A185,TextData!A:A))</f>
-        <v>キュアパッシブ</v>
+        <v>リレイズ</v>
       </c>
       <c r="C185">
-        <v>2010</v>
+        <v>3010</v>
       </c>
       <c r="D185" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C185,Define!P:P))</f>
-        <v>Hp回復</v>
+        <v>ステート付与</v>
       </c>
       <c r="E185">
-        <v>10</v>
+        <v>2450</v>
       </c>
       <c r="F185">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G185">
         <v>1</v>
@@ -48848,24 +48845,27 @@
       <c r="H185">
         <v>100</v>
       </c>
+      <c r="I185" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="186" spans="1:8">
       <c r="A186">
-        <v>14060</v>
+        <v>14100</v>
       </c>
       <c r="B186" t="str">
         <f>INDEX(TextData!B:B,MATCH(A186,TextData!A:A))</f>
-        <v>パッシブサプライ</v>
+        <v>ファストヒール</v>
       </c>
       <c r="C186">
-        <v>4020</v>
+        <v>2010</v>
       </c>
       <c r="D186" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C186,Define!P:P))</f>
-        <v>Ct回復</v>
+        <v>Hp回復</v>
       </c>
       <c r="E186">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F186">
         <v>0</v>
@@ -48877,26 +48877,26 @@
         <v>100</v>
       </c>
     </row>
-    <row r="187" spans="1:9">
+    <row r="187" spans="1:8">
       <c r="A187">
-        <v>14070</v>
+        <v>14110</v>
       </c>
       <c r="B187" t="str">
         <f>INDEX(TextData!B:B,MATCH(A187,TextData!A:A))</f>
-        <v>ホーミングクルセイド</v>
+        <v>リフレッシュ</v>
       </c>
       <c r="C187">
-        <v>3010</v>
+        <v>3060</v>
       </c>
       <c r="D187" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C187,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>デバフステート解除</v>
       </c>
       <c r="E187">
-        <v>2240</v>
+        <v>0</v>
       </c>
       <c r="F187">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G187">
         <v>0</v>
@@ -48904,17 +48904,14 @@
       <c r="H187">
         <v>100</v>
       </c>
-      <c r="I187" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="188" spans="1:9">
       <c r="A188">
-        <v>14090</v>
+        <v>14120</v>
       </c>
       <c r="B188" t="str">
         <f>INDEX(TextData!B:B,MATCH(A188,TextData!A:A))</f>
-        <v>リレイズ</v>
+        <v>ファストメディック</v>
       </c>
       <c r="C188">
         <v>3010</v>
@@ -48924,41 +48921,41 @@
         <v>ステート付与</v>
       </c>
       <c r="E188">
-        <v>2450</v>
+        <v>2040</v>
       </c>
       <c r="F188">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G188">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H188">
         <v>100</v>
       </c>
       <c r="I188" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="189" spans="1:8">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9">
       <c r="A189">
-        <v>14100</v>
+        <v>14130</v>
       </c>
       <c r="B189" t="str">
         <f>INDEX(TextData!B:B,MATCH(A189,TextData!A:A))</f>
-        <v>ファストヒール</v>
+        <v>ディバインシールド</v>
       </c>
       <c r="C189">
-        <v>2010</v>
+        <v>3010</v>
       </c>
       <c r="D189" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C189,Define!P:P))</f>
-        <v>Hp回復</v>
+        <v>ステート付与</v>
       </c>
       <c r="E189">
-        <v>3</v>
+        <v>2180</v>
       </c>
       <c r="F189">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G189">
         <v>0</v>
@@ -48966,30 +48963,33 @@
       <c r="H189">
         <v>100</v>
       </c>
+      <c r="I189" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="190" spans="1:8">
       <c r="A190">
-        <v>14110</v>
+        <v>14140</v>
       </c>
       <c r="B190" t="str">
         <f>INDEX(TextData!B:B,MATCH(A190,TextData!A:A))</f>
-        <v>リフレッシュ</v>
+        <v>ライフディバイド</v>
       </c>
       <c r="C190">
-        <v>3060</v>
+        <v>2040</v>
       </c>
       <c r="D190" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C190,Define!P:P))</f>
-        <v>デバフステート解除</v>
+        <v>Hpを分け与える</v>
       </c>
       <c r="E190">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F190">
         <v>0</v>
       </c>
       <c r="G190">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H190">
         <v>100</v>
@@ -48997,11 +48997,11 @@
     </row>
     <row r="191" spans="1:9">
       <c r="A191">
-        <v>14120</v>
+        <v>14930</v>
       </c>
       <c r="B191" t="str">
         <f>INDEX(TextData!B:B,MATCH(A191,TextData!A:A))</f>
-        <v>ファストメディック</v>
+        <v>エイミングスコープ</v>
       </c>
       <c r="C191">
         <v>3010</v>
@@ -49011,28 +49011,28 @@
         <v>ステート付与</v>
       </c>
       <c r="E191">
-        <v>2040</v>
+        <v>1081</v>
       </c>
       <c r="F191">
-        <v>3</v>
+        <v>999</v>
       </c>
       <c r="G191">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H191">
         <v>100</v>
       </c>
       <c r="I191" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
     </row>
     <row r="192" spans="1:9">
       <c r="A192">
-        <v>14130</v>
+        <v>14940</v>
       </c>
       <c r="B192" t="str">
         <f>INDEX(TextData!B:B,MATCH(A192,TextData!A:A))</f>
-        <v>ディバインシールド</v>
+        <v>リジェネレーション</v>
       </c>
       <c r="C192">
         <v>3010</v>
@@ -49042,56 +49042,59 @@
         <v>ステート付与</v>
       </c>
       <c r="E192">
-        <v>2180</v>
+        <v>2040</v>
       </c>
       <c r="F192">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="G192">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H192">
         <v>100</v>
       </c>
       <c r="I192" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="193" spans="1:8">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9">
       <c r="A193">
-        <v>14920</v>
+        <v>15010</v>
       </c>
       <c r="B193" t="str">
         <f>INDEX(TextData!B:B,MATCH(A193,TextData!A:A))</f>
-        <v>ライフディバイド</v>
+        <v>ワンスパニッシュ</v>
       </c>
       <c r="C193">
-        <v>2040</v>
+        <v>3010</v>
       </c>
       <c r="D193" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C193,Define!P:P))</f>
-        <v>Hpを分け与える</v>
+        <v>ステート付与</v>
       </c>
       <c r="E193">
-        <v>25</v>
+        <v>2050</v>
       </c>
       <c r="F193">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G193">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H193">
         <v>100</v>
       </c>
+      <c r="I193" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="194" spans="1:9">
       <c r="A194">
-        <v>14930</v>
+        <v>15020</v>
       </c>
       <c r="B194" t="str">
         <f>INDEX(TextData!B:B,MATCH(A194,TextData!A:A))</f>
-        <v>エイミングスコープ</v>
+        <v>クイックカース</v>
       </c>
       <c r="C194">
         <v>3010</v>
@@ -49101,28 +49104,28 @@
         <v>ステート付与</v>
       </c>
       <c r="E194">
-        <v>1081</v>
+        <v>1043</v>
       </c>
       <c r="F194">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="G194">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H194">
         <v>100</v>
       </c>
       <c r="I194" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="195" spans="1:9">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8">
       <c r="A195">
-        <v>14940</v>
+        <v>15030</v>
       </c>
       <c r="B195" t="str">
         <f>INDEX(TextData!B:B,MATCH(A195,TextData!A:A))</f>
-        <v>リジェネレーション</v>
+        <v>バイタリティ</v>
       </c>
       <c r="C195">
         <v>3010</v>
@@ -49132,28 +49135,25 @@
         <v>ステート付与</v>
       </c>
       <c r="E195">
-        <v>2040</v>
+        <v>2290</v>
       </c>
       <c r="F195">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="G195">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="H195">
         <v>100</v>
       </c>
-      <c r="I195" t="s">
-        <v>58</v>
-      </c>
     </row>
     <row r="196" spans="1:9">
       <c r="A196">
-        <v>15010</v>
+        <v>15040</v>
       </c>
       <c r="B196" t="str">
         <f>INDEX(TextData!B:B,MATCH(A196,TextData!A:A))</f>
-        <v>ワンスパニッシュ</v>
+        <v>ネガティブドレイン</v>
       </c>
       <c r="C196">
         <v>3010</v>
@@ -49163,75 +49163,72 @@
         <v>ステート付与</v>
       </c>
       <c r="E196">
-        <v>2050</v>
+        <v>2060</v>
       </c>
       <c r="F196">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G196">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H196">
         <v>100</v>
       </c>
       <c r="I196" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="197" spans="1:9">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8">
       <c r="A197">
-        <v>15020</v>
+        <v>15050</v>
       </c>
       <c r="B197" t="str">
         <f>INDEX(TextData!B:B,MATCH(A197,TextData!A:A))</f>
-        <v>クイックカース</v>
+        <v>キュアシェイド</v>
       </c>
       <c r="C197">
-        <v>3010</v>
+        <v>3020</v>
       </c>
       <c r="D197" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C197,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>ステート解除</v>
       </c>
       <c r="E197">
-        <v>1043</v>
+        <v>2020</v>
       </c>
       <c r="F197">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G197">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H197">
         <v>100</v>
       </c>
-      <c r="I197" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="198" spans="1:8">
       <c r="A198">
-        <v>15030</v>
+        <v>15050</v>
       </c>
       <c r="B198" t="str">
         <f>INDEX(TextData!B:B,MATCH(A198,TextData!A:A))</f>
-        <v>バイタリティ</v>
+        <v>キュアシェイド</v>
       </c>
       <c r="C198">
-        <v>3010</v>
+        <v>2010</v>
       </c>
       <c r="D198" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C198,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Hp回復</v>
       </c>
       <c r="E198">
-        <v>2290</v>
+        <v>10</v>
       </c>
       <c r="F198">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G198">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="H198">
         <v>100</v>
@@ -49239,11 +49236,11 @@
     </row>
     <row r="199" spans="1:9">
       <c r="A199">
-        <v>15040</v>
+        <v>15060</v>
       </c>
       <c r="B199" t="str">
         <f>INDEX(TextData!B:B,MATCH(A199,TextData!A:A))</f>
-        <v>ネガティブドレイン</v>
+        <v>アンデッドペイン</v>
       </c>
       <c r="C199">
         <v>3010</v>
@@ -49253,115 +49250,118 @@
         <v>ステート付与</v>
       </c>
       <c r="E199">
-        <v>2060</v>
+        <v>2270</v>
       </c>
       <c r="F199">
         <v>0</v>
       </c>
       <c r="G199">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H199">
         <v>100</v>
       </c>
       <c r="I199" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="200" spans="1:8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9">
       <c r="A200">
-        <v>15050</v>
+        <v>15070</v>
       </c>
       <c r="B200" t="str">
         <f>INDEX(TextData!B:B,MATCH(A200,TextData!A:A))</f>
-        <v>キュアシェイド</v>
+        <v>ジャックポッド</v>
       </c>
       <c r="C200">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="D200" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C200,Define!P:P))</f>
-        <v>ステート解除</v>
+        <v>ステート付与</v>
       </c>
       <c r="E200">
-        <v>2020</v>
+        <v>1070</v>
       </c>
       <c r="F200">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G200">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H200">
         <v>100</v>
       </c>
-    </row>
-    <row r="201" spans="1:8">
+      <c r="I200" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9">
       <c r="A201">
-        <v>15050</v>
+        <v>15070</v>
       </c>
       <c r="B201" t="str">
         <f>INDEX(TextData!B:B,MATCH(A201,TextData!A:A))</f>
-        <v>キュアシェイド</v>
+        <v>ジャックポッド</v>
       </c>
       <c r="C201">
-        <v>2010</v>
+        <v>3010</v>
       </c>
       <c r="D201" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C201,Define!P:P))</f>
-        <v>Hp回復</v>
+        <v>ステート付与</v>
       </c>
       <c r="E201">
-        <v>10</v>
+        <v>1082</v>
       </c>
       <c r="F201">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G201">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H201">
         <v>100</v>
       </c>
-    </row>
-    <row r="202" spans="1:9">
+      <c r="I201" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8">
       <c r="A202">
-        <v>15060</v>
+        <v>15080</v>
       </c>
       <c r="B202" t="str">
         <f>INDEX(TextData!B:B,MATCH(A202,TextData!A:A))</f>
-        <v>アンデッドペイン</v>
+        <v>ヒールハント</v>
       </c>
       <c r="C202">
-        <v>3010</v>
+        <v>1100</v>
       </c>
       <c r="D202" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C202,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Hp貫通ダメージ、Param2でKind指定可</v>
       </c>
       <c r="E202">
-        <v>2270</v>
+        <v>100</v>
       </c>
       <c r="F202">
         <v>0</v>
       </c>
       <c r="G202">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="H202">
         <v>100</v>
       </c>
-      <c r="I202" t="s">
-        <v>45</v>
-      </c>
     </row>
     <row r="203" spans="1:9">
       <c r="A203">
-        <v>15070</v>
+        <v>15110</v>
       </c>
       <c r="B203" t="str">
         <f>INDEX(TextData!B:B,MATCH(A203,TextData!A:A))</f>
-        <v>ジャックポッド</v>
+        <v>フォーカサイト</v>
       </c>
       <c r="C203">
         <v>3010</v>
@@ -49371,87 +49371,87 @@
         <v>ステート付与</v>
       </c>
       <c r="E203">
-        <v>1070</v>
+        <v>2240</v>
       </c>
       <c r="F203">
         <v>1</v>
       </c>
       <c r="G203">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H203">
         <v>100</v>
       </c>
       <c r="I203" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="204" spans="1:9">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8">
       <c r="A204">
-        <v>15070</v>
+        <v>15120</v>
       </c>
       <c r="B204" t="str">
         <f>INDEX(TextData!B:B,MATCH(A204,TextData!A:A))</f>
-        <v>ジャックポッド</v>
+        <v>ガードハント</v>
       </c>
       <c r="C204">
-        <v>3010</v>
+        <v>1100</v>
       </c>
       <c r="D204" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C204,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Hp貫通ダメージ、Param2でKind指定可</v>
       </c>
       <c r="E204">
-        <v>1082</v>
+        <v>100</v>
       </c>
       <c r="F204">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G204">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H204">
         <v>100</v>
       </c>
-      <c r="I204" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="205" spans="1:8">
+    </row>
+    <row r="205" spans="1:9">
       <c r="A205">
-        <v>15080</v>
+        <v>15130</v>
       </c>
       <c r="B205" t="str">
         <f>INDEX(TextData!B:B,MATCH(A205,TextData!A:A))</f>
-        <v>ヒールハント</v>
+        <v>リヴェンジャー</v>
       </c>
       <c r="C205">
-        <v>1100</v>
+        <v>3010</v>
       </c>
       <c r="D205" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C205,Define!P:P))</f>
-        <v>Hp貫通ダメージ、Param2でKind指定可</v>
+        <v>ステート付与</v>
       </c>
       <c r="E205">
-        <v>100</v>
+        <v>1040</v>
       </c>
       <c r="F205">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G205">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="H205">
         <v>100</v>
       </c>
+      <c r="I205" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="206" spans="1:9">
       <c r="A206">
-        <v>15110</v>
+        <v>15130</v>
       </c>
       <c r="B206" t="str">
         <f>INDEX(TextData!B:B,MATCH(A206,TextData!A:A))</f>
-        <v>フォーカサイト</v>
+        <v>リヴェンジャー</v>
       </c>
       <c r="C206">
         <v>3010</v>
@@ -49461,87 +49461,87 @@
         <v>ステート付与</v>
       </c>
       <c r="E206">
-        <v>2240</v>
+        <v>1050</v>
       </c>
       <c r="F206">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G206">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H206">
         <v>100</v>
       </c>
       <c r="I206" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="207" spans="1:8">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9">
       <c r="A207">
-        <v>15120</v>
+        <v>15140</v>
       </c>
       <c r="B207" t="str">
         <f>INDEX(TextData!B:B,MATCH(A207,TextData!A:A))</f>
-        <v>ガードハント</v>
+        <v>ソーサリーコネクト</v>
       </c>
       <c r="C207">
-        <v>1100</v>
+        <v>3010</v>
       </c>
       <c r="D207" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C207,Define!P:P))</f>
-        <v>Hp貫通ダメージ、Param2でKind指定可</v>
+        <v>ステート付与</v>
       </c>
       <c r="E207">
-        <v>100</v>
+        <v>1040</v>
       </c>
       <c r="F207">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G207">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="H207">
         <v>100</v>
       </c>
-    </row>
-    <row r="208" spans="1:9">
+      <c r="I207" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8">
       <c r="A208">
-        <v>15130</v>
+        <v>15140</v>
       </c>
       <c r="B208" t="str">
         <f>INDEX(TextData!B:B,MATCH(A208,TextData!A:A))</f>
-        <v>リヴェンジャー</v>
+        <v>ソーサリーコネクト</v>
       </c>
       <c r="C208">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D208" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C208,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E208">
-        <v>1040</v>
+        <v>12071</v>
       </c>
       <c r="F208">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G208">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H208">
         <v>100</v>
       </c>
-      <c r="I208" t="s">
-        <v>49</v>
-      </c>
     </row>
     <row r="209" spans="1:9">
       <c r="A209">
-        <v>15130</v>
+        <v>15141</v>
       </c>
       <c r="B209" t="str">
         <f>INDEX(TextData!B:B,MATCH(A209,TextData!A:A))</f>
-        <v>リヴェンジャー</v>
+        <v>ソーサリーコネクト</v>
       </c>
       <c r="C209">
         <v>3010</v>
@@ -49551,19 +49551,19 @@
         <v>ステート付与</v>
       </c>
       <c r="E209">
-        <v>1050</v>
+        <v>1041</v>
       </c>
       <c r="F209">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G209">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H209">
         <v>100</v>
       </c>
       <c r="I209" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="210" spans="1:8">
@@ -59086,21 +59086,21 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37">
-        <v>12070</v>
+        <v>12090</v>
       </c>
       <c r="B37" t="str">
         <f>INDEX(TextData!B:B,MATCH(A37,TextData!A:A))</f>
-        <v>ソーサリーコネクト</v>
+        <v>アウトオブオーダー</v>
       </c>
       <c r="C37">
-        <v>15011</v>
+        <v>0</v>
       </c>
       <c r="D37" t="str">
         <f>INDEX(Define!V:V,MATCH(C37,Define!U:U))</f>
-        <v>味方が攻撃タイプの行動をしようとしている</v>
+        <v>なし</v>
       </c>
       <c r="E37">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -59114,30 +59114,30 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38">
-        <v>12090</v>
+        <v>12100</v>
       </c>
       <c r="B38" t="str">
         <f>INDEX(TextData!B:B,MATCH(A38,TextData!A:A))</f>
-        <v>アウトオブオーダー</v>
+        <v>ワンスパニッシュ</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>12060</v>
       </c>
       <c r="D38" t="str">
         <f>INDEX(Define!V:V,MATCH(C38,Define!U:U))</f>
-        <v>なし</v>
+        <v>味方が攻撃を受ける。Param2で対象指定</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="F38">
         <v>0</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -59149,45 +59149,45 @@
         <v>ワンスパニッシュ</v>
       </c>
       <c r="C39">
-        <v>12060</v>
+        <v>11010</v>
       </c>
       <c r="D39" t="str">
         <f>INDEX(Define!V:V,MATCH(C39,Define!U:U))</f>
-        <v>味方が攻撃を受ける。Param2で対象指定</v>
+        <v>バトル中使用回数が〇以下</v>
       </c>
       <c r="E39">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H39">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40">
-        <v>12100</v>
+        <v>12110</v>
       </c>
       <c r="B40" t="str">
         <f>INDEX(TextData!B:B,MATCH(A40,TextData!A:A))</f>
-        <v>ワンスパニッシュ</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="C40">
-        <v>11010</v>
+        <v>15010</v>
       </c>
       <c r="D40" t="str">
         <f>INDEX(Define!V:V,MATCH(C40,Define!U:U))</f>
-        <v>バトル中使用回数が〇以下</v>
+        <v>自身が攻撃タイプの行動をしようとしている</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -59198,27 +59198,27 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41">
-        <v>12110</v>
+        <v>12120</v>
       </c>
       <c r="B41" t="str">
         <f>INDEX(TextData!B:B,MATCH(A41,TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>パリィ</v>
       </c>
       <c r="C41">
-        <v>15010</v>
+        <v>12060</v>
       </c>
       <c r="D41" t="str">
         <f>INDEX(Define!V:V,MATCH(C41,Define!U:U))</f>
-        <v>自身が攻撃タイプの行動をしようとしている</v>
+        <v>味方が攻撃を受ける。Param2で対象指定</v>
       </c>
       <c r="E41">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F41">
         <v>0</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -59226,27 +59226,27 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42">
-        <v>12120</v>
+        <v>12130</v>
       </c>
       <c r="B42" t="str">
         <f>INDEX(TextData!B:B,MATCH(A42,TextData!A:A))</f>
-        <v>パリィ</v>
+        <v>チェイスマジック</v>
       </c>
       <c r="C42">
-        <v>12060</v>
+        <v>12071</v>
       </c>
       <c r="D42" t="str">
         <f>INDEX(Define!V:V,MATCH(C42,Define!U:U))</f>
-        <v>味方が攻撃を受ける。Param2で対象指定</v>
+        <v>味方が攻撃を成功する</v>
       </c>
       <c r="E42">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="F42">
         <v>0</v>
       </c>
       <c r="G42">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -59254,18 +59254,18 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43">
-        <v>12130</v>
+        <v>12140</v>
       </c>
       <c r="B43" t="str">
         <f>INDEX(TextData!B:B,MATCH(A43,TextData!A:A))</f>
-        <v>チェイスマジック</v>
+        <v>ウィンドライズ</v>
       </c>
       <c r="C43">
-        <v>12071</v>
+        <v>23010</v>
       </c>
       <c r="D43" t="str">
         <f>INDEX(Define!V:V,MATCH(C43,Define!U:U))</f>
-        <v>味方が攻撃を成功する</v>
+        <v>攻撃を回避した時</v>
       </c>
       <c r="E43">
         <v>61</v>
@@ -59282,21 +59282,21 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44">
-        <v>12140</v>
+        <v>12510</v>
       </c>
       <c r="B44" t="str">
         <f>INDEX(TextData!B:B,MATCH(A44,TextData!A:A))</f>
-        <v>ウィンドライズ</v>
+        <v>アクトスタンス</v>
       </c>
       <c r="C44">
-        <v>23010</v>
+        <v>0</v>
       </c>
       <c r="D44" t="str">
         <f>INDEX(Define!V:V,MATCH(C44,Define!U:U))</f>
-        <v>攻撃を回避した時</v>
+        <v>なし</v>
       </c>
       <c r="E44">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -59310,11 +59310,11 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45">
-        <v>12510</v>
+        <v>12910</v>
       </c>
       <c r="B45" t="str">
         <f>INDEX(TextData!B:B,MATCH(A45,TextData!A:A))</f>
-        <v>アクトスタンス</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -59338,11 +59338,11 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46">
-        <v>12910</v>
+        <v>12930</v>
       </c>
       <c r="B46" t="str">
         <f>INDEX(TextData!B:B,MATCH(A46,TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>スウィフトカレント</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -59366,11 +59366,11 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47">
-        <v>12930</v>
+        <v>12940</v>
       </c>
       <c r="B47" t="str">
         <f>INDEX(TextData!B:B,MATCH(A47,TextData!A:A))</f>
-        <v>スウィフトカレント</v>
+        <v>イヴェイドオール</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -59394,27 +59394,27 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48">
-        <v>12940</v>
+        <v>13010</v>
       </c>
       <c r="B48" t="str">
         <f>INDEX(TextData!B:B,MATCH(A48,TextData!A:A))</f>
-        <v>イヴェイドオール</v>
+        <v>ヘビィカバー</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>12010</v>
       </c>
       <c r="D48" t="str">
         <f>INDEX(Define!V:V,MATCH(C48,Define!U:U))</f>
-        <v>なし</v>
+        <v>かばうが成立する</v>
       </c>
       <c r="E48">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="F48">
         <v>0</v>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H48">
         <v>0</v>
@@ -59422,27 +59422,27 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49">
-        <v>13010</v>
+        <v>13011</v>
       </c>
       <c r="B49" t="str">
         <f>INDEX(TextData!B:B,MATCH(A49,TextData!A:A))</f>
         <v>ヘビィカバー</v>
       </c>
       <c r="C49">
-        <v>12010</v>
+        <v>0</v>
       </c>
       <c r="D49" t="str">
         <f>INDEX(Define!V:V,MATCH(C49,Define!U:U))</f>
-        <v>かばうが成立する</v>
+        <v>なし</v>
       </c>
       <c r="E49">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="F49">
         <v>0</v>
       </c>
       <c r="G49">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H49">
         <v>0</v>
@@ -59450,24 +59450,24 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50">
-        <v>13011</v>
+        <v>13020</v>
       </c>
       <c r="B50" t="str">
         <f>INDEX(TextData!B:B,MATCH(A50,TextData!A:A))</f>
-        <v>ヘビィカバー</v>
+        <v>アイシクルエッジ</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>10010</v>
       </c>
       <c r="D50" t="str">
         <f>INDEX(Define!V:V,MATCH(C50,Define!U:U))</f>
-        <v>なし</v>
+        <v>攻撃成功時〇%で</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="F50">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -59478,27 +59478,27 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51">
-        <v>13020</v>
+        <v>13030</v>
       </c>
       <c r="B51" t="str">
         <f>INDEX(TextData!B:B,MATCH(A51,TextData!A:A))</f>
-        <v>アイシクルエッジ</v>
+        <v>カウンターマジック</v>
       </c>
       <c r="C51">
-        <v>10010</v>
+        <v>12060</v>
       </c>
       <c r="D51" t="str">
         <f>INDEX(Define!V:V,MATCH(C51,Define!U:U))</f>
-        <v>攻撃成功時〇%で</v>
+        <v>味方が攻撃を受ける。Param2で対象指定</v>
       </c>
       <c r="E51">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="F51">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H51">
         <v>0</v>
@@ -59506,27 +59506,27 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52">
-        <v>13030</v>
+        <v>13040</v>
       </c>
       <c r="B52" t="str">
         <f>INDEX(TextData!B:B,MATCH(A52,TextData!A:A))</f>
-        <v>カウンターマジック</v>
+        <v>アーマーコード</v>
       </c>
       <c r="C52">
-        <v>12060</v>
+        <v>0</v>
       </c>
       <c r="D52" t="str">
         <f>INDEX(Define!V:V,MATCH(C52,Define!U:U))</f>
-        <v>味方が攻撃を受ける。Param2で対象指定</v>
+        <v>なし</v>
       </c>
       <c r="E52">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F52">
         <v>0</v>
       </c>
       <c r="G52">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H52">
         <v>0</v>
@@ -59534,21 +59534,21 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53">
-        <v>13040</v>
+        <v>13050</v>
       </c>
       <c r="B53" t="str">
         <f>INDEX(TextData!B:B,MATCH(A53,TextData!A:A))</f>
-        <v>アーマーコード</v>
+        <v>キュアフリーズ</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>12064</v>
       </c>
       <c r="D53" t="str">
         <f>INDEX(Define!V:V,MATCH(C53,Define!U:U))</f>
-        <v>なし</v>
+        <v>味方が状態異常を受ける。Param2で対象指定。Param3でState指定</v>
       </c>
       <c r="E53">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -59557,57 +59557,57 @@
         <v>0</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54">
-        <v>13050</v>
+        <v>13070</v>
       </c>
       <c r="B54" t="str">
         <f>INDEX(TextData!B:B,MATCH(A54,TextData!A:A))</f>
-        <v>キュアフリーズ</v>
+        <v>アシッドラッシュ</v>
       </c>
       <c r="C54">
-        <v>12064</v>
+        <v>10010</v>
       </c>
       <c r="D54" t="str">
         <f>INDEX(Define!V:V,MATCH(C54,Define!U:U))</f>
-        <v>味方が状態異常を受ける。Param2で対象指定。Param3でState指定</v>
+        <v>攻撃成功時〇%で</v>
       </c>
       <c r="E54">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="F54">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G54">
         <v>0</v>
       </c>
       <c r="H54">
-        <v>2140</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55">
-        <v>13070</v>
+        <v>13090</v>
       </c>
       <c r="B55" t="str">
         <f>INDEX(TextData!B:B,MATCH(A55,TextData!A:A))</f>
-        <v>アシッドラッシュ</v>
+        <v>アイスセイバー</v>
       </c>
       <c r="C55">
-        <v>10010</v>
+        <v>10110</v>
       </c>
       <c r="D55" t="str">
         <f>INDEX(Define!V:V,MATCH(C55,Define!U:U))</f>
-        <v>攻撃成功時〇%で</v>
+        <v>攻撃成功時相手が凍結ではない</v>
       </c>
       <c r="E55">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="F55">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -59616,29 +59616,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" ht="12" customHeight="1" spans="1:8">
       <c r="A56">
-        <v>13090</v>
+        <v>13110</v>
       </c>
       <c r="B56" t="str">
         <f>INDEX(TextData!B:B,MATCH(A56,TextData!A:A))</f>
-        <v>アイスセイバー</v>
+        <v>ガーディアン</v>
       </c>
       <c r="C56">
-        <v>10110</v>
+        <v>12060</v>
       </c>
       <c r="D56" t="str">
         <f>INDEX(Define!V:V,MATCH(C56,Define!U:U))</f>
-        <v>攻撃成功時相手が凍結ではない</v>
+        <v>味方が攻撃を受ける。Param2で対象指定</v>
       </c>
       <c r="E56">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="F56">
         <v>0</v>
       </c>
       <c r="G56">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H56">
         <v>0</v>
@@ -59646,18 +59646,18 @@
     </row>
     <row r="57" ht="12" customHeight="1" spans="1:8">
       <c r="A57">
-        <v>13110</v>
+        <v>13120</v>
       </c>
       <c r="B57" t="str">
         <f>INDEX(TextData!B:B,MATCH(A57,TextData!A:A))</f>
-        <v>ガーディアン</v>
+        <v>ライフセーブ</v>
       </c>
       <c r="C57">
-        <v>12060</v>
+        <v>20160</v>
       </c>
       <c r="D57" t="str">
         <f>INDEX(Define!V:V,MATCH(C57,Define!U:U))</f>
-        <v>味方が攻撃を受ける。Param2で対象指定</v>
+        <v>自身が戦闘不能になる攻撃を受ける</v>
       </c>
       <c r="E57">
         <v>31</v>
@@ -59666,13 +59666,13 @@
         <v>0</v>
       </c>
       <c r="G57">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" ht="12" customHeight="1" spans="1:8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
       <c r="A58">
         <v>13120</v>
       </c>
@@ -59681,45 +59681,45 @@
         <v>ライフセーブ</v>
       </c>
       <c r="C58">
-        <v>20160</v>
+        <v>11010</v>
       </c>
       <c r="D58" t="str">
         <f>INDEX(Define!V:V,MATCH(C58,Define!U:U))</f>
-        <v>自身が戦闘不能になる攻撃を受ける</v>
+        <v>バトル中使用回数が〇以下</v>
       </c>
       <c r="E58">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G58">
         <v>0</v>
       </c>
       <c r="H58">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59">
-        <v>13120</v>
+        <v>13130</v>
       </c>
       <c r="B59" t="str">
         <f>INDEX(TextData!B:B,MATCH(A59,TextData!A:A))</f>
-        <v>ライフセーブ</v>
+        <v>ライフスティール</v>
       </c>
       <c r="C59">
-        <v>11010</v>
+        <v>15010</v>
       </c>
       <c r="D59" t="str">
         <f>INDEX(Define!V:V,MATCH(C59,Define!U:U))</f>
-        <v>バトル中使用回数が〇以下</v>
+        <v>自身が攻撃タイプの行動をしようとしている</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -59730,21 +59730,21 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60">
-        <v>13130</v>
+        <v>13140</v>
       </c>
       <c r="B60" t="str">
         <f>INDEX(TextData!B:B,MATCH(A60,TextData!A:A))</f>
-        <v>ライフスティール</v>
+        <v>クイックバリア</v>
       </c>
       <c r="C60">
-        <v>15010</v>
+        <v>12060</v>
       </c>
       <c r="D60" t="str">
         <f>INDEX(Define!V:V,MATCH(C60,Define!U:U))</f>
-        <v>自身が攻撃タイプの行動をしようとしている</v>
+        <v>味方が攻撃を受ける。Param2で対象指定</v>
       </c>
       <c r="E60">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -59898,21 +59898,21 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66">
-        <v>13920</v>
+        <v>13930</v>
       </c>
       <c r="B66" t="str">
         <f>INDEX(TextData!B:B,MATCH(A66,TextData!A:A))</f>
-        <v>クイックバリア</v>
+        <v>クイックキュア</v>
       </c>
       <c r="C66">
-        <v>12060</v>
+        <v>12042</v>
       </c>
       <c r="D66" t="str">
         <f>INDEX(Define!V:V,MATCH(C66,Define!U:U))</f>
-        <v>味方が攻撃を受ける。Param2で対象指定</v>
+        <v>攻撃を受けた対象がAbnorml状態になった</v>
       </c>
       <c r="E66">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -59924,57 +59924,57 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" ht="12" customHeight="1" spans="1:8">
       <c r="A67">
-        <v>13930</v>
+        <v>13940</v>
       </c>
       <c r="B67" t="str">
         <f>INDEX(TextData!B:B,MATCH(A67,TextData!A:A))</f>
-        <v>クイックキュア</v>
+        <v>セルフシールド</v>
       </c>
       <c r="C67">
-        <v>12042</v>
+        <v>12060</v>
       </c>
       <c r="D67" t="str">
         <f>INDEX(Define!V:V,MATCH(C67,Define!U:U))</f>
-        <v>攻撃を受けた対象がAbnorml状態になった</v>
+        <v>味方が攻撃を受ける。Param2で対象指定</v>
       </c>
       <c r="E67">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="F67">
         <v>0</v>
       </c>
       <c r="G67">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H67">
         <v>0</v>
       </c>
     </row>
-    <row r="68" ht="12" customHeight="1" spans="1:8">
+    <row r="68" spans="1:8">
       <c r="A68">
-        <v>13940</v>
+        <v>13950</v>
       </c>
       <c r="B68" t="str">
         <f>INDEX(TextData!B:B,MATCH(A68,TextData!A:A))</f>
-        <v>セルフシールド</v>
+        <v>パッシブジャミング</v>
       </c>
       <c r="C68">
-        <v>12060</v>
+        <v>15022</v>
       </c>
       <c r="D68" t="str">
         <f>INDEX(Define!V:V,MATCH(C68,Define!U:U))</f>
-        <v>味方が攻撃を受ける。Param2で対象指定</v>
+        <v>相手がバフの行動をしようとしている</v>
       </c>
       <c r="E68">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F68">
         <v>0</v>
       </c>
       <c r="G68">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H68">
         <v>0</v>
@@ -59982,30 +59982,30 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69">
-        <v>13950</v>
+        <v>14010</v>
       </c>
       <c r="B69" t="str">
         <f>INDEX(TextData!B:B,MATCH(A69,TextData!A:A))</f>
-        <v>パッシブジャミング</v>
+        <v>ファーストエイド</v>
       </c>
       <c r="C69">
-        <v>15022</v>
+        <v>1130</v>
       </c>
       <c r="D69" t="str">
         <f>INDEX(Define!V:V,MATCH(C69,Define!U:U))</f>
-        <v>相手がバフの行動をしようとしている</v>
+        <v>最もHpが少ない味方</v>
       </c>
       <c r="E69">
-        <v>23</v>
+        <v>101</v>
       </c>
       <c r="F69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69">
         <v>0</v>
       </c>
       <c r="H69">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -60017,51 +60017,51 @@
         <v>ファーストエイド</v>
       </c>
       <c r="C70">
-        <v>1130</v>
+        <v>11011</v>
       </c>
       <c r="D70" t="str">
         <f>INDEX(Define!V:V,MATCH(C70,Define!U:U))</f>
-        <v>最もHpが少ない味方</v>
+        <v>Period中使用回数が〇以下</v>
       </c>
       <c r="E70">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="F70">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G70">
         <v>0</v>
       </c>
       <c r="H70">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71">
-        <v>14010</v>
+        <v>14020</v>
       </c>
       <c r="B71" t="str">
         <f>INDEX(TextData!B:B,MATCH(A71,TextData!A:A))</f>
-        <v>ファーストエイド</v>
+        <v>クイックヒール</v>
       </c>
       <c r="C71">
-        <v>11011</v>
+        <v>12040</v>
       </c>
       <c r="D71" t="str">
         <f>INDEX(Define!V:V,MATCH(C71,Define!U:U))</f>
-        <v>Period中使用回数が〇以下</v>
+        <v>攻撃を受けた対象のHpがParam1%以下 Param2==1で生存判定しない</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F71">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="G71">
         <v>0</v>
       </c>
       <c r="H71">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -60073,23 +60073,23 @@
         <v>クイックヒール</v>
       </c>
       <c r="C72">
-        <v>12040</v>
+        <v>18010</v>
       </c>
       <c r="D72" t="str">
         <f>INDEX(Define!V:V,MATCH(C72,Define!U:U))</f>
-        <v>攻撃を受けた対象のHpがParam1%以下 Param2==1で生存判定しない</v>
+        <v>自分の味方である</v>
       </c>
       <c r="E72">
         <v>11</v>
       </c>
       <c r="F72">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G72">
         <v>0</v>
       </c>
       <c r="H72">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -60101,17 +60101,17 @@
         <v>クイックヒール</v>
       </c>
       <c r="C73">
-        <v>18010</v>
+        <v>11011</v>
       </c>
       <c r="D73" t="str">
         <f>INDEX(Define!V:V,MATCH(C73,Define!U:U))</f>
-        <v>自分の味方である</v>
+        <v>Period中使用回数が〇以下</v>
       </c>
       <c r="E73">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F73">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -60122,24 +60122,24 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74">
-        <v>14020</v>
+        <v>14030</v>
       </c>
       <c r="B74" t="str">
         <f>INDEX(TextData!B:B,MATCH(A74,TextData!A:A))</f>
-        <v>クイックヒール</v>
+        <v>ガードバインド</v>
       </c>
       <c r="C74">
-        <v>11011</v>
+        <v>15010</v>
       </c>
       <c r="D74" t="str">
         <f>INDEX(Define!V:V,MATCH(C74,Define!U:U))</f>
-        <v>Period中使用回数が〇以下</v>
+        <v>自身が攻撃タイプの行動をしようとしている</v>
       </c>
       <c r="E74">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F74">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -60150,21 +60150,21 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75">
-        <v>14030</v>
+        <v>14040</v>
       </c>
       <c r="B75" t="str">
         <f>INDEX(TextData!B:B,MATCH(A75,TextData!A:A))</f>
-        <v>ガードバインド</v>
+        <v>ホープフルアイリス</v>
       </c>
       <c r="C75">
-        <v>15010</v>
+        <v>0</v>
       </c>
       <c r="D75" t="str">
         <f>INDEX(Define!V:V,MATCH(C75,Define!U:U))</f>
-        <v>自身が攻撃タイプの行動をしようとしている</v>
+        <v>なし</v>
       </c>
       <c r="E75">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F75">
         <v>0</v>
@@ -60178,21 +60178,21 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76">
-        <v>14040</v>
+        <v>14050</v>
       </c>
       <c r="B76" t="str">
         <f>INDEX(TextData!B:B,MATCH(A76,TextData!A:A))</f>
-        <v>ホープフルアイリス</v>
+        <v>キュアパッシブ</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>12064</v>
       </c>
       <c r="D76" t="str">
         <f>INDEX(Define!V:V,MATCH(C76,Define!U:U))</f>
-        <v>なし</v>
+        <v>味方が状態異常を受ける。Param2で対象指定。Param3でState指定</v>
       </c>
       <c r="E76">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -60201,26 +60201,26 @@
         <v>0</v>
       </c>
       <c r="H76">
-        <v>0</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77">
-        <v>14050</v>
+        <v>14060</v>
       </c>
       <c r="B77" t="str">
         <f>INDEX(TextData!B:B,MATCH(A77,TextData!A:A))</f>
-        <v>キュアパッシブ</v>
+        <v>パッシブサプライ</v>
       </c>
       <c r="C77">
-        <v>12064</v>
+        <v>12066</v>
       </c>
       <c r="D77" t="str">
         <f>INDEX(Define!V:V,MATCH(C77,Define!U:U))</f>
-        <v>味方が状態異常を受ける。Param2で対象指定。Param3でState指定</v>
+        <v>自身がパッシブを受ける</v>
       </c>
       <c r="E77">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -60229,7 +60229,7 @@
         <v>0</v>
       </c>
       <c r="H77">
-        <v>2090</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -60241,45 +60241,45 @@
         <v>パッシブサプライ</v>
       </c>
       <c r="C78">
-        <v>12066</v>
+        <v>11020</v>
       </c>
       <c r="D78" t="str">
         <f>INDEX(Define!V:V,MATCH(C78,Define!U:U))</f>
-        <v>自身がパッシブを受ける</v>
+        <v>ターン中使用回数が〇回に満たない</v>
       </c>
       <c r="E78">
         <v>61</v>
       </c>
       <c r="F78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78">
         <v>0</v>
       </c>
       <c r="H78">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79">
-        <v>14060</v>
+        <v>14070</v>
       </c>
       <c r="B79" t="str">
         <f>INDEX(TextData!B:B,MATCH(A79,TextData!A:A))</f>
-        <v>パッシブサプライ</v>
+        <v>ホーミングクルセイド</v>
       </c>
       <c r="C79">
-        <v>11020</v>
+        <v>0</v>
       </c>
       <c r="D79" t="str">
         <f>INDEX(Define!V:V,MATCH(C79,Define!U:U))</f>
-        <v>ターン中使用回数が〇回に満たない</v>
+        <v>なし</v>
       </c>
       <c r="E79">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="F79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -60290,21 +60290,21 @@
     </row>
     <row r="80" spans="1:8">
       <c r="A80">
-        <v>14070</v>
+        <v>14090</v>
       </c>
       <c r="B80" t="str">
         <f>INDEX(TextData!B:B,MATCH(A80,TextData!A:A))</f>
-        <v>ホーミングクルセイド</v>
+        <v>リレイズ</v>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>20050</v>
       </c>
       <c r="D80" t="str">
         <f>INDEX(Define!V:V,MATCH(C80,Define!U:U))</f>
-        <v>なし</v>
+        <v>自身が戦闘不能になる</v>
       </c>
       <c r="E80">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -60318,21 +60318,21 @@
     </row>
     <row r="81" spans="1:8">
       <c r="A81">
-        <v>14090</v>
+        <v>14100</v>
       </c>
       <c r="B81" t="str">
         <f>INDEX(TextData!B:B,MATCH(A81,TextData!A:A))</f>
-        <v>リレイズ</v>
+        <v>ファストヒール</v>
       </c>
       <c r="C81">
-        <v>20050</v>
+        <v>0</v>
       </c>
       <c r="D81" t="str">
         <f>INDEX(Define!V:V,MATCH(C81,Define!U:U))</f>
-        <v>自身が戦闘不能になる</v>
+        <v>なし</v>
       </c>
       <c r="E81">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -60346,21 +60346,21 @@
     </row>
     <row r="82" spans="1:8">
       <c r="A82">
-        <v>14100</v>
+        <v>14110</v>
       </c>
       <c r="B82" t="str">
         <f>INDEX(TextData!B:B,MATCH(A82,TextData!A:A))</f>
-        <v>ファストヒール</v>
+        <v>リフレッシュ</v>
       </c>
       <c r="C82">
-        <v>0</v>
+        <v>12064</v>
       </c>
       <c r="D82" t="str">
         <f>INDEX(Define!V:V,MATCH(C82,Define!U:U))</f>
-        <v>なし</v>
+        <v>味方が状態異常を受ける。Param2で対象指定。Param3でState指定</v>
       </c>
       <c r="E82">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -60374,21 +60374,21 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83">
-        <v>14110</v>
+        <v>14120</v>
       </c>
       <c r="B83" t="str">
         <f>INDEX(TextData!B:B,MATCH(A83,TextData!A:A))</f>
-        <v>リフレッシュ</v>
+        <v>ファストメディック</v>
       </c>
       <c r="C83">
-        <v>12064</v>
+        <v>0</v>
       </c>
       <c r="D83" t="str">
         <f>INDEX(Define!V:V,MATCH(C83,Define!U:U))</f>
-        <v>味方が状態異常を受ける。Param2で対象指定。Param3でState指定</v>
+        <v>なし</v>
       </c>
       <c r="E83">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -60402,11 +60402,11 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84">
-        <v>14120</v>
+        <v>14130</v>
       </c>
       <c r="B84" t="str">
         <f>INDEX(TextData!B:B,MATCH(A84,TextData!A:A))</f>
-        <v>ファストメディック</v>
+        <v>ディバインシールド</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -60430,52 +60430,52 @@
     </row>
     <row r="85" spans="1:8">
       <c r="A85">
-        <v>14130</v>
+        <v>14140</v>
       </c>
       <c r="B85" t="str">
         <f>INDEX(TextData!B:B,MATCH(A85,TextData!A:A))</f>
-        <v>ディバインシールド</v>
+        <v>ライフディバイド</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>12040</v>
       </c>
       <c r="D85" t="str">
         <f>INDEX(Define!V:V,MATCH(C85,Define!U:U))</f>
-        <v>なし</v>
+        <v>攻撃を受けた対象のHpがParam1%以下 Param2==1で生存判定しない</v>
       </c>
       <c r="E85">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G85">
         <v>0</v>
       </c>
       <c r="H85">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86">
-        <v>14920</v>
+        <v>14140</v>
       </c>
       <c r="B86" t="str">
         <f>INDEX(TextData!B:B,MATCH(A86,TextData!A:A))</f>
         <v>ライフディバイド</v>
       </c>
       <c r="C86">
-        <v>12040</v>
+        <v>1020</v>
       </c>
       <c r="D86" t="str">
         <f>INDEX(Define!V:V,MATCH(C86,Define!U:U))</f>
-        <v>攻撃を受けた対象のHpがParam1%以下 Param2==1で生存判定しない</v>
+        <v>自身のHpが〇%以上</v>
       </c>
       <c r="E86">
         <v>11</v>
       </c>
       <c r="F86">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -60486,49 +60486,49 @@
     </row>
     <row r="87" spans="1:8">
       <c r="A87">
-        <v>14920</v>
+        <v>14140</v>
       </c>
       <c r="B87" t="str">
         <f>INDEX(TextData!B:B,MATCH(A87,TextData!A:A))</f>
         <v>ライフディバイド</v>
       </c>
       <c r="C87">
-        <v>1020</v>
+        <v>9120</v>
       </c>
       <c r="D87" t="str">
         <f>INDEX(Define!V:V,MATCH(C87,Define!U:U))</f>
-        <v>自身のHpが〇%以上</v>
+        <v>自身を対象にしない</v>
       </c>
       <c r="E87">
         <v>11</v>
       </c>
       <c r="F87">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G87">
         <v>0</v>
       </c>
       <c r="H87">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88">
-        <v>14920</v>
+        <v>14930</v>
       </c>
       <c r="B88" t="str">
         <f>INDEX(TextData!B:B,MATCH(A88,TextData!A:A))</f>
-        <v>ライフディバイド</v>
+        <v>エイミングスコープ</v>
       </c>
       <c r="C88">
-        <v>9120</v>
+        <v>0</v>
       </c>
       <c r="D88" t="str">
         <f>INDEX(Define!V:V,MATCH(C88,Define!U:U))</f>
-        <v>自身を対象にしない</v>
+        <v>なし</v>
       </c>
       <c r="E88">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -60542,11 +60542,11 @@
     </row>
     <row r="89" spans="1:8">
       <c r="A89">
-        <v>14930</v>
+        <v>14940</v>
       </c>
       <c r="B89" t="str">
         <f>INDEX(TextData!B:B,MATCH(A89,TextData!A:A))</f>
-        <v>エイミングスコープ</v>
+        <v>リジェネレーション</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -60570,30 +60570,30 @@
     </row>
     <row r="90" spans="1:8">
       <c r="A90">
-        <v>14940</v>
+        <v>15010</v>
       </c>
       <c r="B90" t="str">
         <f>INDEX(TextData!B:B,MATCH(A90,TextData!A:A))</f>
-        <v>リジェネレーション</v>
+        <v>ワンスパニッシュ</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>12060</v>
       </c>
       <c r="D90" t="str">
         <f>INDEX(Define!V:V,MATCH(C90,Define!U:U))</f>
-        <v>なし</v>
+        <v>味方が攻撃を受ける。Param2で対象指定</v>
       </c>
       <c r="E90">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="F90">
         <v>0</v>
       </c>
       <c r="G90">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H90">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -60605,45 +60605,45 @@
         <v>ワンスパニッシュ</v>
       </c>
       <c r="C91">
-        <v>12060</v>
+        <v>11010</v>
       </c>
       <c r="D91" t="str">
         <f>INDEX(Define!V:V,MATCH(C91,Define!U:U))</f>
-        <v>味方が攻撃を受ける。Param2で対象指定</v>
+        <v>バトル中使用回数が〇以下</v>
       </c>
       <c r="E91">
         <v>31</v>
       </c>
       <c r="F91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G91">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H91">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92">
-        <v>15010</v>
+        <v>15020</v>
       </c>
       <c r="B92" t="str">
         <f>INDEX(TextData!B:B,MATCH(A92,TextData!A:A))</f>
-        <v>ワンスパニッシュ</v>
+        <v>クイックカース</v>
       </c>
       <c r="C92">
-        <v>11010</v>
+        <v>12060</v>
       </c>
       <c r="D92" t="str">
         <f>INDEX(Define!V:V,MATCH(C92,Define!U:U))</f>
-        <v>バトル中使用回数が〇以下</v>
+        <v>味方が攻撃を受ける。Param2で対象指定</v>
       </c>
       <c r="E92">
         <v>31</v>
       </c>
       <c r="F92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -60654,21 +60654,21 @@
     </row>
     <row r="93" spans="1:8">
       <c r="A93">
-        <v>15020</v>
+        <v>15030</v>
       </c>
       <c r="B93" t="str">
         <f>INDEX(TextData!B:B,MATCH(A93,TextData!A:A))</f>
-        <v>クイックカース</v>
+        <v>バイタリティ</v>
       </c>
       <c r="C93">
-        <v>12060</v>
+        <v>15010</v>
       </c>
       <c r="D93" t="str">
         <f>INDEX(Define!V:V,MATCH(C93,Define!U:U))</f>
-        <v>味方が攻撃を受ける。Param2で対象指定</v>
+        <v>自身が攻撃タイプの行動をしようとしている</v>
       </c>
       <c r="E93">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F93">
         <v>0</v>
@@ -60677,7 +60677,7 @@
         <v>0</v>
       </c>
       <c r="H93">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -60689,45 +60689,45 @@
         <v>バイタリティ</v>
       </c>
       <c r="C94">
-        <v>15010</v>
+        <v>1020</v>
       </c>
       <c r="D94" t="str">
         <f>INDEX(Define!V:V,MATCH(C94,Define!U:U))</f>
-        <v>自身が攻撃タイプの行動をしようとしている</v>
+        <v>自身のHpが〇%以上</v>
       </c>
       <c r="E94">
         <v>21</v>
       </c>
       <c r="F94">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G94">
         <v>0</v>
       </c>
       <c r="H94">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95">
-        <v>15030</v>
+        <v>15040</v>
       </c>
       <c r="B95" t="str">
         <f>INDEX(TextData!B:B,MATCH(A95,TextData!A:A))</f>
-        <v>バイタリティ</v>
+        <v>ネガティブドレイン</v>
       </c>
       <c r="C95">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="D95" t="str">
         <f>INDEX(Define!V:V,MATCH(C95,Define!U:U))</f>
-        <v>自身のHpが〇%以上</v>
+        <v>自身のHpが〇%以下</v>
       </c>
       <c r="E95">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="F95">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -60738,49 +60738,49 @@
     </row>
     <row r="96" spans="1:8">
       <c r="A96">
-        <v>15040</v>
+        <v>15050</v>
       </c>
       <c r="B96" t="str">
         <f>INDEX(TextData!B:B,MATCH(A96,TextData!A:A))</f>
-        <v>ネガティブドレイン</v>
+        <v>キュアシェイド</v>
       </c>
       <c r="C96">
-        <v>1010</v>
+        <v>12064</v>
       </c>
       <c r="D96" t="str">
         <f>INDEX(Define!V:V,MATCH(C96,Define!U:U))</f>
-        <v>自身のHpが〇%以下</v>
+        <v>味方が状態異常を受ける。Param2で対象指定。Param3でState指定</v>
       </c>
       <c r="E96">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="F96">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G96">
         <v>0</v>
       </c>
       <c r="H96">
-        <v>0</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="97" spans="1:8">
       <c r="A97">
-        <v>15050</v>
+        <v>15060</v>
       </c>
       <c r="B97" t="str">
         <f>INDEX(TextData!B:B,MATCH(A97,TextData!A:A))</f>
-        <v>キュアシェイド</v>
+        <v>アンデッドペイン</v>
       </c>
       <c r="C97">
-        <v>12064</v>
+        <v>0</v>
       </c>
       <c r="D97" t="str">
         <f>INDEX(Define!V:V,MATCH(C97,Define!U:U))</f>
-        <v>味方が状態異常を受ける。Param2で対象指定。Param3でState指定</v>
+        <v>なし</v>
       </c>
       <c r="E97">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F97">
         <v>0</v>
@@ -60789,26 +60789,26 @@
         <v>0</v>
       </c>
       <c r="H97">
-        <v>2020</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98">
-        <v>15060</v>
+        <v>15070</v>
       </c>
       <c r="B98" t="str">
         <f>INDEX(TextData!B:B,MATCH(A98,TextData!A:A))</f>
-        <v>アンデッドペイン</v>
+        <v>ジャックポッド</v>
       </c>
       <c r="C98">
-        <v>0</v>
+        <v>15011</v>
       </c>
       <c r="D98" t="str">
         <f>INDEX(Define!V:V,MATCH(C98,Define!U:U))</f>
-        <v>なし</v>
+        <v>味方が攻撃タイプの行動をしようとしている</v>
       </c>
       <c r="E98">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="F98">
         <v>0</v>
@@ -60822,21 +60822,21 @@
     </row>
     <row r="99" spans="1:8">
       <c r="A99">
-        <v>15070</v>
+        <v>15080</v>
       </c>
       <c r="B99" t="str">
         <f>INDEX(TextData!B:B,MATCH(A99,TextData!A:A))</f>
-        <v>ジャックポッド</v>
+        <v>ヒールハント</v>
       </c>
       <c r="C99">
-        <v>15011</v>
+        <v>12082</v>
       </c>
       <c r="D99" t="str">
         <f>INDEX(Define!V:V,MATCH(C99,Define!U:U))</f>
-        <v>味方が攻撃タイプの行動をしようとしている</v>
+        <v>相手が回復をする</v>
       </c>
       <c r="E99">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="F99">
         <v>0</v>
@@ -60850,21 +60850,21 @@
     </row>
     <row r="100" spans="1:8">
       <c r="A100">
-        <v>15080</v>
+        <v>15110</v>
       </c>
       <c r="B100" t="str">
         <f>INDEX(TextData!B:B,MATCH(A100,TextData!A:A))</f>
-        <v>ヒールハント</v>
+        <v>フォーカサイト</v>
       </c>
       <c r="C100">
-        <v>12082</v>
+        <v>15011</v>
       </c>
       <c r="D100" t="str">
         <f>INDEX(Define!V:V,MATCH(C100,Define!U:U))</f>
-        <v>相手が回復をする</v>
+        <v>味方が攻撃タイプの行動をしようとしている</v>
       </c>
       <c r="E100">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="F100">
         <v>0</v>
@@ -60878,27 +60878,27 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101">
-        <v>15110</v>
+        <v>15120</v>
       </c>
       <c r="B101" t="str">
         <f>INDEX(TextData!B:B,MATCH(A101,TextData!A:A))</f>
-        <v>フォーカサイト</v>
+        <v>ガードハント</v>
       </c>
       <c r="C101">
-        <v>15011</v>
+        <v>12011</v>
       </c>
       <c r="D101" t="str">
         <f>INDEX(Define!V:V,MATCH(C101,Define!U:U))</f>
-        <v>味方が攻撃タイプの行動をしようとしている</v>
+        <v>かばう成立後かばった対象</v>
       </c>
       <c r="E101">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="F101">
         <v>0</v>
       </c>
       <c r="G101">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H101">
         <v>0</v>
@@ -60906,27 +60906,27 @@
     </row>
     <row r="102" spans="1:8">
       <c r="A102">
-        <v>15120</v>
+        <v>15130</v>
       </c>
       <c r="B102" t="str">
         <f>INDEX(TextData!B:B,MATCH(A102,TextData!A:A))</f>
-        <v>ガードハント</v>
+        <v>リヴェンジャー</v>
       </c>
       <c r="C102">
-        <v>12011</v>
+        <v>12060</v>
       </c>
       <c r="D102" t="str">
         <f>INDEX(Define!V:V,MATCH(C102,Define!U:U))</f>
-        <v>かばう成立後かばった対象</v>
+        <v>味方が攻撃を受ける。Param2で対象指定</v>
       </c>
       <c r="E102">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="F102">
         <v>0</v>
       </c>
       <c r="G102">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H102">
         <v>0</v>
@@ -60934,27 +60934,27 @@
     </row>
     <row r="103" spans="1:8">
       <c r="A103">
-        <v>15130</v>
+        <v>15140</v>
       </c>
       <c r="B103" t="str">
         <f>INDEX(TextData!B:B,MATCH(A103,TextData!A:A))</f>
-        <v>リヴェンジャー</v>
+        <v>ソーサリーコネクト</v>
       </c>
       <c r="C103">
-        <v>12060</v>
+        <v>15011</v>
       </c>
       <c r="D103" t="str">
         <f>INDEX(Define!V:V,MATCH(C103,Define!U:U))</f>
-        <v>味方が攻撃を受ける。Param2で対象指定</v>
+        <v>味方が攻撃タイプの行動をしようとしている</v>
       </c>
       <c r="E103">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F103">
         <v>0</v>
       </c>
       <c r="G103">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H103">
         <v>0</v>
@@ -66224,7 +66224,7 @@
     </row>
     <row r="102" ht="39" spans="1:7">
       <c r="A102">
-        <v>12070</v>
+        <v>12090</v>
       </c>
       <c r="B102" t="s">
         <v>441</v>
@@ -66239,9 +66239,9 @@
         <v>444</v>
       </c>
     </row>
-    <row r="103" ht="39" spans="1:7">
+    <row r="103" customFormat="1" ht="39" spans="1:7">
       <c r="A103">
-        <v>12090</v>
+        <v>12100</v>
       </c>
       <c r="B103" t="s">
         <v>445</v>
@@ -66258,41 +66258,41 @@
     </row>
     <row r="104" customFormat="1" ht="39" spans="1:7">
       <c r="A104">
-        <v>12100</v>
+        <v>12110</v>
       </c>
       <c r="B104" t="s">
+        <v>153</v>
+      </c>
+      <c r="C104" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="C104" s="3" t="s">
+      <c r="F104" t="s">
+        <v>155</v>
+      </c>
+      <c r="G104" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="F104" t="s">
+    </row>
+    <row r="105" customFormat="1" ht="26" spans="1:7">
+      <c r="A105">
+        <v>12120</v>
+      </c>
+      <c r="B105" t="s">
         <v>451</v>
       </c>
-      <c r="G104" s="3" t="s">
+      <c r="C105" s="3" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="105" customFormat="1" ht="39" spans="1:7">
-      <c r="A105">
-        <v>12110</v>
-      </c>
-      <c r="B105" t="s">
-        <v>153</v>
-      </c>
-      <c r="C105" s="3" t="s">
+      <c r="F105" t="s">
         <v>453</v>
-      </c>
-      <c r="F105" t="s">
-        <v>155</v>
       </c>
       <c r="G105" s="3" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="106" customFormat="1" ht="26" spans="1:7">
+    <row r="106" ht="26" spans="1:7">
       <c r="A106">
-        <v>12120</v>
+        <v>12130</v>
       </c>
       <c r="B106" t="s">
         <v>455</v>
@@ -66309,7 +66309,7 @@
     </row>
     <row r="107" ht="26" spans="1:7">
       <c r="A107">
-        <v>12130</v>
+        <v>12140</v>
       </c>
       <c r="B107" t="s">
         <v>459</v>
@@ -66324,9 +66324,9 @@
         <v>462</v>
       </c>
     </row>
-    <row r="108" ht="26" spans="1:7">
+    <row r="108" customFormat="1" ht="39" spans="1:7">
       <c r="A108">
-        <v>12140</v>
+        <v>12510</v>
       </c>
       <c r="B108" t="s">
         <v>463</v>
@@ -66341,43 +66341,43 @@
         <v>466</v>
       </c>
     </row>
-    <row r="109" customFormat="1" ht="39" spans="1:7">
+    <row r="109" spans="1:7">
       <c r="A109">
-        <v>12510</v>
+        <v>12910</v>
       </c>
       <c r="B109" t="s">
+        <v>153</v>
+      </c>
+      <c r="C109" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="C109" s="3" t="s">
+      <c r="F109" t="s">
+        <v>155</v>
+      </c>
+      <c r="G109" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="F109" t="s">
+    </row>
+    <row r="110" ht="26" spans="1:7">
+      <c r="A110">
+        <v>12930</v>
+      </c>
+      <c r="B110" t="s">
         <v>469</v>
       </c>
-      <c r="G109" s="3" t="s">
+      <c r="C110" s="3" t="s">
         <v>470</v>
       </c>
-    </row>
-    <row r="110" spans="1:7">
-      <c r="A110">
-        <v>12910</v>
-      </c>
-      <c r="B110" t="s">
-        <v>153</v>
-      </c>
-      <c r="C110" s="3" t="s">
+      <c r="F110" t="s">
         <v>471</v>
-      </c>
-      <c r="F110" t="s">
-        <v>155</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="111" ht="26" spans="1:7">
+    <row r="111" ht="39" spans="1:7">
       <c r="A111">
-        <v>12930</v>
+        <v>12940</v>
       </c>
       <c r="B111" t="s">
         <v>473</v>
@@ -66394,7 +66394,7 @@
     </row>
     <row r="112" ht="39" spans="1:7">
       <c r="A112">
-        <v>12940</v>
+        <v>13010</v>
       </c>
       <c r="B112" t="s">
         <v>477</v>
@@ -66411,7 +66411,7 @@
     </row>
     <row r="113" ht="39" spans="1:7">
       <c r="A113">
-        <v>13010</v>
+        <v>13020</v>
       </c>
       <c r="B113" t="s">
         <v>481</v>
@@ -66426,9 +66426,9 @@
         <v>484</v>
       </c>
     </row>
-    <row r="114" ht="39" spans="1:7">
+    <row r="114" ht="26" spans="1:7">
       <c r="A114">
-        <v>13020</v>
+        <v>13030</v>
       </c>
       <c r="B114" t="s">
         <v>485</v>
@@ -66445,7 +66445,7 @@
     </row>
     <row r="115" ht="26" spans="1:7">
       <c r="A115">
-        <v>13030</v>
+        <v>13040</v>
       </c>
       <c r="B115" t="s">
         <v>489</v>
@@ -66462,41 +66462,41 @@
     </row>
     <row r="116" ht="26" spans="1:7">
       <c r="A116">
-        <v>13040</v>
+        <v>13050</v>
       </c>
       <c r="B116" t="s">
         <v>493</v>
       </c>
-      <c r="C116" s="3" t="s">
+      <c r="C116" s="4" t="s">
         <v>494</v>
       </c>
       <c r="F116" t="s">
         <v>495</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>496</v>
+        <v>437</v>
       </c>
     </row>
     <row r="117" ht="26" spans="1:7">
       <c r="A117">
-        <v>13050</v>
+        <v>13070</v>
       </c>
       <c r="B117" t="s">
+        <v>496</v>
+      </c>
+      <c r="C117" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="C117" s="4" t="s">
+      <c r="F117" t="s">
         <v>498</v>
       </c>
-      <c r="F117" t="s">
+      <c r="G117" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="G117" s="3" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="118" ht="26" spans="1:7">
+    </row>
+    <row r="118" ht="52" spans="1:7">
       <c r="A118">
-        <v>13070</v>
+        <v>13090</v>
       </c>
       <c r="B118" t="s">
         <v>500</v>
@@ -66511,9 +66511,9 @@
         <v>503</v>
       </c>
     </row>
-    <row r="119" ht="52" spans="1:7">
+    <row r="119" customFormat="1" ht="26" spans="1:7">
       <c r="A119">
-        <v>13090</v>
+        <v>13110</v>
       </c>
       <c r="B119" t="s">
         <v>504</v>
@@ -66528,9 +66528,9 @@
         <v>507</v>
       </c>
     </row>
-    <row r="120" customFormat="1" ht="26" spans="1:7">
+    <row r="120" customFormat="1" ht="39" spans="1:7">
       <c r="A120">
-        <v>13110</v>
+        <v>13120</v>
       </c>
       <c r="B120" t="s">
         <v>508</v>
@@ -66545,9 +66545,9 @@
         <v>511</v>
       </c>
     </row>
-    <row r="121" customFormat="1" ht="39" spans="1:7">
+    <row r="121" ht="26" spans="1:7">
       <c r="A121">
-        <v>13120</v>
+        <v>13130</v>
       </c>
       <c r="B121" t="s">
         <v>512</v>
@@ -66564,7 +66564,7 @@
     </row>
     <row r="122" ht="26" spans="1:7">
       <c r="A122">
-        <v>13130</v>
+        <v>13140</v>
       </c>
       <c r="B122" t="s">
         <v>516</v>
@@ -66664,9 +66664,9 @@
         <v>535</v>
       </c>
     </row>
-    <row r="128" ht="26" spans="1:7">
+    <row r="128" ht="39" spans="1:7">
       <c r="A128">
-        <v>13920</v>
+        <v>13930</v>
       </c>
       <c r="B128" t="s">
         <v>536</v>
@@ -66681,9 +66681,9 @@
         <v>539</v>
       </c>
     </row>
-    <row r="129" ht="39" spans="1:7">
+    <row r="129" ht="26" spans="1:7">
       <c r="A129">
-        <v>13930</v>
+        <v>13940</v>
       </c>
       <c r="B129" t="s">
         <v>540</v>
@@ -66698,9 +66698,9 @@
         <v>543</v>
       </c>
     </row>
-    <row r="130" ht="26" spans="1:7">
+    <row r="130" ht="39" spans="1:7">
       <c r="A130">
-        <v>13940</v>
+        <v>13950</v>
       </c>
       <c r="B130" t="s">
         <v>544</v>
@@ -66715,9 +66715,9 @@
         <v>547</v>
       </c>
     </row>
-    <row r="131" ht="39" spans="1:7">
+    <row r="131" customFormat="1" ht="39" spans="1:7">
       <c r="A131">
-        <v>13950</v>
+        <v>14010</v>
       </c>
       <c r="B131" t="s">
         <v>548</v>
@@ -66732,9 +66732,9 @@
         <v>551</v>
       </c>
     </row>
-    <row r="132" customFormat="1" ht="39" spans="1:7">
+    <row r="132" ht="39" spans="1:7">
       <c r="A132">
-        <v>14010</v>
+        <v>14020</v>
       </c>
       <c r="B132" t="s">
         <v>552</v>
@@ -66749,9 +66749,9 @@
         <v>555</v>
       </c>
     </row>
-    <row r="133" ht="39" spans="1:7">
+    <row r="133" ht="26" spans="1:7">
       <c r="A133">
-        <v>14020</v>
+        <v>14030</v>
       </c>
       <c r="B133" t="s">
         <v>556</v>
@@ -66768,7 +66768,7 @@
     </row>
     <row r="134" ht="26" spans="1:7">
       <c r="A134">
-        <v>14030</v>
+        <v>14040</v>
       </c>
       <c r="B134" t="s">
         <v>560</v>
@@ -66785,41 +66785,41 @@
     </row>
     <row r="135" ht="26" spans="1:7">
       <c r="A135">
-        <v>14040</v>
+        <v>14050</v>
       </c>
       <c r="B135" t="s">
         <v>564</v>
       </c>
-      <c r="C135" s="3" t="s">
+      <c r="C135" s="4" t="s">
         <v>565</v>
       </c>
       <c r="F135" t="s">
         <v>566</v>
       </c>
       <c r="G135" s="3" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="136" ht="39" spans="1:7">
+      <c r="A136">
+        <v>14060</v>
+      </c>
+      <c r="B136" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="136" ht="26" spans="1:7">
-      <c r="A136">
-        <v>14050</v>
-      </c>
-      <c r="B136" t="s">
+      <c r="C136" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="C136" s="4" t="s">
+      <c r="F136" t="s">
         <v>569</v>
       </c>
-      <c r="F136" t="s">
+      <c r="G136" s="3" t="s">
         <v>570</v>
-      </c>
-      <c r="G136" s="3" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="137" ht="39" spans="1:7">
       <c r="A137">
-        <v>14060</v>
+        <v>14070</v>
       </c>
       <c r="B137" t="s">
         <v>571</v>
@@ -66836,7 +66836,7 @@
     </row>
     <row r="138" ht="39" spans="1:7">
       <c r="A138">
-        <v>14070</v>
+        <v>14090</v>
       </c>
       <c r="B138" t="s">
         <v>575</v>
@@ -66844,24 +66844,24 @@
       <c r="C138" s="3" t="s">
         <v>576</v>
       </c>
+      <c r="D138" t="s">
+        <v>577</v>
+      </c>
       <c r="F138" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="139" ht="39" spans="1:7">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="139" customFormat="1" ht="26" spans="1:7">
       <c r="A139">
-        <v>14090</v>
+        <v>14100</v>
       </c>
       <c r="B139" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>580</v>
-      </c>
-      <c r="D139" t="s">
         <v>581</v>
       </c>
       <c r="F139" t="s">
@@ -66873,7 +66873,7 @@
     </row>
     <row r="140" customFormat="1" ht="26" spans="1:7">
       <c r="A140">
-        <v>14100</v>
+        <v>14110</v>
       </c>
       <c r="B140" t="s">
         <v>584</v>
@@ -66890,7 +66890,7 @@
     </row>
     <row r="141" customFormat="1" ht="26" spans="1:7">
       <c r="A141">
-        <v>14110</v>
+        <v>14120</v>
       </c>
       <c r="B141" t="s">
         <v>588</v>
@@ -66905,9 +66905,9 @@
         <v>591</v>
       </c>
     </row>
-    <row r="142" customFormat="1" ht="26" spans="1:7">
+    <row r="142" ht="39" spans="1:7">
       <c r="A142">
-        <v>14120</v>
+        <v>14130</v>
       </c>
       <c r="B142" t="s">
         <v>592</v>
@@ -66924,7 +66924,7 @@
     </row>
     <row r="143" ht="39" spans="1:7">
       <c r="A143">
-        <v>14130</v>
+        <v>14140</v>
       </c>
       <c r="B143" t="s">
         <v>596</v>
@@ -66939,9 +66939,9 @@
         <v>599</v>
       </c>
     </row>
-    <row r="144" ht="39" spans="1:7">
+    <row r="144" ht="26" spans="1:7">
       <c r="A144">
-        <v>14920</v>
+        <v>14930</v>
       </c>
       <c r="B144" t="s">
         <v>600</v>
@@ -66956,60 +66956,60 @@
         <v>603</v>
       </c>
     </row>
-    <row r="145" ht="26" spans="1:7">
+    <row r="145" spans="1:7">
       <c r="A145">
-        <v>14930</v>
+        <v>14940</v>
       </c>
       <c r="B145" t="s">
         <v>604</v>
       </c>
-      <c r="C145" s="3" t="s">
+      <c r="C145" t="s">
         <v>605</v>
       </c>
       <c r="F145" t="s">
         <v>606</v>
       </c>
-      <c r="G145" s="3" t="s">
+      <c r="G145" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="146" spans="1:7">
+    <row r="146" customFormat="1" ht="39" spans="1:7">
       <c r="A146">
-        <v>14940</v>
+        <v>15010</v>
       </c>
       <c r="B146" t="s">
+        <v>445</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="F146" t="s">
+        <v>447</v>
+      </c>
+      <c r="G146" s="3" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="147" ht="26" spans="1:7">
+      <c r="A147">
+        <v>15020</v>
+      </c>
+      <c r="B147" t="s">
         <v>608</v>
       </c>
-      <c r="C146" t="s">
+      <c r="C147" s="3" t="s">
         <v>609</v>
       </c>
-      <c r="F146" t="s">
+      <c r="F147" t="s">
         <v>610</v>
       </c>
-      <c r="G146" t="s">
+      <c r="G147" s="3" t="s">
         <v>611</v>
-      </c>
-    </row>
-    <row r="147" customFormat="1" ht="39" spans="1:7">
-      <c r="A147">
-        <v>15010</v>
-      </c>
-      <c r="B147" t="s">
-        <v>449</v>
-      </c>
-      <c r="C147" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="F147" t="s">
-        <v>451</v>
-      </c>
-      <c r="G147" s="3" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="148" ht="26" spans="1:7">
       <c r="A148">
-        <v>15020</v>
+        <v>15030</v>
       </c>
       <c r="B148" t="s">
         <v>612</v>
@@ -67026,7 +67026,7 @@
     </row>
     <row r="149" ht="26" spans="1:7">
       <c r="A149">
-        <v>15030</v>
+        <v>15040</v>
       </c>
       <c r="B149" t="s">
         <v>616</v>
@@ -67043,41 +67043,41 @@
     </row>
     <row r="150" ht="26" spans="1:7">
       <c r="A150">
-        <v>15040</v>
+        <v>15050</v>
       </c>
       <c r="B150" t="s">
         <v>620</v>
       </c>
-      <c r="C150" s="3" t="s">
+      <c r="C150" s="4" t="s">
         <v>621</v>
       </c>
       <c r="F150" t="s">
         <v>622</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="151" ht="26" spans="1:7">
       <c r="A151">
-        <v>15050</v>
+        <v>15060</v>
       </c>
       <c r="B151" t="s">
+        <v>623</v>
+      </c>
+      <c r="C151" s="3" t="s">
         <v>624</v>
       </c>
-      <c r="C151" s="4" t="s">
+      <c r="F151" t="s">
         <v>625</v>
       </c>
-      <c r="F151" t="s">
+      <c r="G151" s="3" t="s">
         <v>626</v>
       </c>
-      <c r="G151" s="3" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="152" ht="26" spans="1:7">
+    </row>
+    <row r="152" ht="39" spans="1:7">
       <c r="A152">
-        <v>15060</v>
+        <v>15070</v>
       </c>
       <c r="B152" t="s">
         <v>627</v>
@@ -67085,24 +67085,24 @@
       <c r="C152" s="3" t="s">
         <v>628</v>
       </c>
+      <c r="D152" t="s">
+        <v>629</v>
+      </c>
       <c r="F152" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="153" ht="39" spans="1:7">
       <c r="A153">
-        <v>15070</v>
+        <v>15080</v>
       </c>
       <c r="B153" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>632</v>
-      </c>
-      <c r="D153" t="s">
         <v>633</v>
       </c>
       <c r="F153" t="s">
@@ -67112,9 +67112,9 @@
         <v>635</v>
       </c>
     </row>
-    <row r="154" ht="39" spans="1:7">
+    <row r="154" customFormat="1" ht="26" spans="1:7">
       <c r="A154">
-        <v>15080</v>
+        <v>15110</v>
       </c>
       <c r="B154" t="s">
         <v>636</v>
@@ -67129,9 +67129,9 @@
         <v>639</v>
       </c>
     </row>
-    <row r="155" customFormat="1" ht="26" spans="1:7">
+    <row r="155" customFormat="1" ht="39" spans="1:7">
       <c r="A155">
-        <v>15110</v>
+        <v>15120</v>
       </c>
       <c r="B155" t="s">
         <v>640</v>
@@ -67148,7 +67148,7 @@
     </row>
     <row r="156" customFormat="1" ht="39" spans="1:7">
       <c r="A156">
-        <v>15120</v>
+        <v>15130</v>
       </c>
       <c r="B156" t="s">
         <v>644</v>
@@ -67163,9 +67163,9 @@
         <v>647</v>
       </c>
     </row>
-    <row r="157" customFormat="1" ht="39" spans="1:7">
+    <row r="157" ht="39" spans="1:7">
       <c r="A157">
-        <v>15130</v>
+        <v>15140</v>
       </c>
       <c r="B157" t="s">
         <v>648</v>
@@ -68515,7 +68515,7 @@
         <v>900</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="F236" t="s">
         <v>901</v>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -347,7 +347,7 @@
   </si>
   <si>
     <t>\sにATKx/f[f,0,1]%ダメージ
-対象を倒した場合/f[f,2,2]ターンATK+f[f,2,3]%</t>
+対象を倒した場合/f[f,2,2]ターンATK+/f[f,2,3]%</t>
   </si>
   <si>
     <t>Finish Stub</t>
@@ -5050,10 +5050,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -5071,29 +5071,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -5108,14 +5085,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -5124,16 +5093,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5155,8 +5139,40 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5169,33 +5185,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5208,8 +5199,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5236,13 +5236,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5254,7 +5278,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5266,73 +5404,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5344,79 +5416,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5464,31 +5464,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5497,7 +5473,18 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5519,11 +5506,24 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5535,145 +5535,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -5101,10 +5101,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -5131,7 +5131,45 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5147,7 +5185,51 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5161,77 +5243,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -5244,23 +5260,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -5287,31 +5287,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5323,13 +5299,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5341,13 +5341,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5359,97 +5359,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5467,7 +5377,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5478,6 +5478,47 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -5496,17 +5537,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5539,42 +5574,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5586,145 +5586,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -46660,7 +46660,7 @@
         <v>Hpダメージ</v>
       </c>
       <c r="E102">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F102">
         <v>0</v>
